--- a/cache/exports/BOQ-Hadrut-generated.xlsx
+++ b/cache/exports/BOQ-Hadrut-generated.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AZ-BOQ\cache\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06B8DE1-BE26-4C3F-A999-1463165013E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4F4BD0-10C1-4A13-A417-9C3EA0688BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOQ" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BOQ!$A$7:$L$2340</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BOQ!$A$1:$L$196</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BOQ!$A$1:$L$193</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">BOQ!$7:$9</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="218">
   <si>
     <t xml:space="preserve">PROJECT / İnşaat obyekti : </t>
   </si>
@@ -241,6 +241,21 @@
     <t>Mərmər tavalardan örtüklərin düzəldilməsi, 1 m²-də tavaların sayı: 3 ədədə qədər (süni mərmər)</t>
   </si>
   <si>
+    <t>2.13</t>
+  </si>
+  <si>
+    <t>4 çıxışlı Yanğın Deposu binası. Daxili su kəməri və kanalizasiya (SO-Ümumi təyinatlı su şəbəkəsi)</t>
+  </si>
+  <si>
+    <t>Polad boruların futlyara salınması, boruların diametri: 100 mm (D114x5.0mm)</t>
+  </si>
+  <si>
+    <t>Sinklənmiş polad su-qaz borularından su təchizatı boru kəmərlərinin çəkilməsi, diametri: 15 mm</t>
+  </si>
+  <si>
+    <t>Qaz-su xətləri üçün şərti keçid diametri 15 mm, divarının qalınlığı 2,8 mm olan sinklənmiş, adi, yivli, qaynaq edilmiş polad borular</t>
+  </si>
+  <si>
     <t>2.19</t>
   </si>
   <si>
@@ -430,6 +445,9 @@
     <t>Yaşayış və ictimai binalarda PVX profildən pəncərə bloklarının qoyulması: açılmıyan, boşluğun sahəsi 2 m²-ə qədər</t>
   </si>
   <si>
+    <t>Hazır boşluqlara metal qapı bloklarının qurulması</t>
+  </si>
+  <si>
     <t>9.8</t>
   </si>
   <si>
@@ -632,27 +650,6 @@
   </si>
   <si>
     <t>Sahənin bölünməsi</t>
-  </si>
-  <si>
-    <t>24.1</t>
-  </si>
-  <si>
-    <t>(Qum meydançası)</t>
-  </si>
-  <si>
-    <t>Dərinliyi 2 m-ə qədər olan yamaclı xəndəklərdə qruntun bərkitmələr olmadan əl ilə qazılması, qruntun qrupu: 1</t>
-  </si>
-  <si>
-    <t>Beton hazırlıq qatının qurulması</t>
-  </si>
-  <si>
-    <t>Beton və daş səthlərin sement-əhəng və ya sement məhlulu ilə suvanması: divarların, sadə</t>
-  </si>
-  <si>
-    <t>Divar və bünövrələrin hidroizolyasiyası: yandan, kərpic, beton və but hörgüsünün düzləndirilmiş səthi üzrə yapışdırıcılı 2 qat</t>
-  </si>
-  <si>
-    <t>Bir lay fanerdan döşəmələrin əsasının qurulması: sahəsi 20m² qədər (faner 18 mm)</t>
   </si>
   <si>
     <t>26.2</t>
@@ -1658,8 +1655,8 @@
         <v>6</v>
       </c>
       <c r="C5" s="14">
-        <f>F194</f>
-        <v>571468.97161479201</v>
+        <f>F191</f>
+        <v>566997.92171106709</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -3353,7 +3350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A50" s="31" t="s">
         <v>67</v>
       </c>
@@ -3383,24 +3380,24 @@
         <v>69</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D51" s="36">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="E51" s="36">
-        <v>508.24360000000001</v>
+        <v>15.440799999999999</v>
       </c>
       <c r="F51" s="36">
         <f>+E51*D51</f>
-        <v>1484.071312</v>
+        <v>41.690159999999999</v>
       </c>
       <c r="G51" s="37">
-        <f>I51+K51</f>
+        <f t="shared" ref="G51:H53" si="9">I51+K51</f>
         <v>0</v>
       </c>
       <c r="H51" s="38">
-        <f>J51+L51</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I51" s="37">
@@ -3418,54 +3415,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="31" t="s">
+    <row r="52" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="33">
+        <v>2</v>
+      </c>
+      <c r="B52" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" s="36">
+        <v>2.7</v>
+      </c>
+      <c r="E52" s="36">
+        <v>5.9446000000000003</v>
+      </c>
+      <c r="F52" s="36">
+        <f>+E52*D52</f>
+        <v>16.050420000000003</v>
+      </c>
+      <c r="G52" s="37">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H52" s="38">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="37">
+        <f>J52/F52</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="38">
+        <v>0</v>
+      </c>
+      <c r="K52" s="37">
+        <f>L52/F52</f>
+        <v>0</v>
+      </c>
+      <c r="L52" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="33">
+        <v>3</v>
+      </c>
+      <c r="B53" s="34" t="s">
         <v>71</v>
-      </c>
-      <c r="B52" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" s="41">
-        <v>0</v>
-      </c>
-      <c r="D52" s="42"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="44"/>
-      <c r="I52" s="43"/>
-      <c r="J52" s="44"/>
-      <c r="K52" s="43"/>
-      <c r="L52" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="33">
-        <v>1</v>
-      </c>
-      <c r="B53" s="34" t="s">
-        <v>73</v>
       </c>
       <c r="C53" s="35" t="s">
         <v>34</v>
       </c>
       <c r="D53" s="36">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="E53" s="36">
-        <v>17.886800000000001</v>
+        <v>2.75</v>
       </c>
       <c r="F53" s="36">
         <f>+E53*D53</f>
-        <v>107.32080000000001</v>
+        <v>7.4250000000000007</v>
       </c>
       <c r="G53" s="37">
-        <f>I53+K53</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H53" s="38">
-        <f>J53+L53</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I53" s="37">
@@ -3485,10 +3503,10 @@
     </row>
     <row r="54" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A54" s="31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B54" s="40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C54" s="41">
         <v>0</v>
@@ -3505,32 +3523,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A55" s="33">
         <v>1</v>
       </c>
       <c r="B55" s="34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D55" s="36">
-        <v>2510</v>
+        <v>2.92</v>
       </c>
       <c r="E55" s="36">
-        <v>0.9</v>
+        <v>508.24360000000001</v>
       </c>
       <c r="F55" s="36">
         <f>+E55*D55</f>
-        <v>2259</v>
+        <v>1484.071312</v>
       </c>
       <c r="G55" s="37">
-        <f t="shared" ref="G55:H57" si="9">I55+K55</f>
+        <f>I55+K55</f>
         <v>0</v>
       </c>
       <c r="H55" s="38">
-        <f t="shared" si="9"/>
+        <f>J55+L55</f>
         <v>0</v>
       </c>
       <c r="I55" s="37">
@@ -3548,52 +3566,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="33">
-        <v>2</v>
-      </c>
-      <c r="B56" s="34" t="s">
+    <row r="56" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="C56" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="D56" s="36">
-        <v>2510</v>
-      </c>
-      <c r="E56" s="36">
-        <v>2.242</v>
-      </c>
-      <c r="F56" s="36">
-        <f>+E56*D56</f>
-        <v>5627.42</v>
-      </c>
-      <c r="G56" s="37">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H56" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="37">
-        <f>J56/F56</f>
-        <v>0</v>
-      </c>
-      <c r="J56" s="38">
-        <v>0</v>
-      </c>
-      <c r="K56" s="37">
-        <f>L56/F56</f>
-        <v>0</v>
-      </c>
-      <c r="L56" s="38">
+      <c r="C56" s="41">
+        <v>0</v>
+      </c>
+      <c r="D56" s="42"/>
+      <c r="E56" s="42"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="43"/>
+      <c r="J56" s="44"/>
+      <c r="K56" s="43"/>
+      <c r="L56" s="44">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A57" s="33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B57" s="34" t="s">
         <v>78</v>
@@ -3602,21 +3599,21 @@
         <v>34</v>
       </c>
       <c r="D57" s="36">
-        <v>2140</v>
+        <v>6</v>
       </c>
       <c r="E57" s="36">
-        <v>6.1</v>
+        <v>17.886800000000001</v>
       </c>
       <c r="F57" s="36">
         <f>+E57*D57</f>
-        <v>13054</v>
+        <v>107.32080000000001</v>
       </c>
       <c r="G57" s="37">
-        <f t="shared" si="9"/>
+        <f>I57+K57</f>
         <v>0</v>
       </c>
       <c r="H57" s="38">
-        <f t="shared" si="9"/>
+        <f>J57+L57</f>
         <v>0</v>
       </c>
       <c r="I57" s="37">
@@ -3634,7 +3631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A58" s="31" t="s">
         <v>79</v>
       </c>
@@ -3667,21 +3664,21 @@
         <v>34</v>
       </c>
       <c r="D59" s="36">
-        <v>1580</v>
+        <v>2510</v>
       </c>
       <c r="E59" s="36">
-        <v>1.1894</v>
+        <v>0.9</v>
       </c>
       <c r="F59" s="36">
         <f>+E59*D59</f>
-        <v>1879.252</v>
+        <v>2259</v>
       </c>
       <c r="G59" s="37">
-        <f>I59+K59</f>
+        <f t="shared" ref="G59:H61" si="10">I59+K59</f>
         <v>0</v>
       </c>
       <c r="H59" s="38">
-        <f>J59+L59</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I59" s="37">
@@ -3699,54 +3696,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="31" t="s">
+    <row r="60" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="33">
+        <v>2</v>
+      </c>
+      <c r="B60" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="B60" s="40" t="s">
+      <c r="C60" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="36">
+        <v>2510</v>
+      </c>
+      <c r="E60" s="36">
+        <v>2.242</v>
+      </c>
+      <c r="F60" s="36">
+        <f>+E60*D60</f>
+        <v>5627.42</v>
+      </c>
+      <c r="G60" s="37">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H60" s="38">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I60" s="37">
+        <f>J60/F60</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="38">
+        <v>0</v>
+      </c>
+      <c r="K60" s="37">
+        <f>L60/F60</f>
+        <v>0</v>
+      </c>
+      <c r="L60" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="33">
+        <v>3</v>
+      </c>
+      <c r="B61" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="C60" s="41">
-        <v>0</v>
-      </c>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="43"/>
-      <c r="H60" s="44"/>
-      <c r="I60" s="43"/>
-      <c r="J60" s="44"/>
-      <c r="K60" s="43"/>
-      <c r="L60" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="33">
-        <v>1</v>
-      </c>
-      <c r="B61" s="34" t="s">
-        <v>84</v>
-      </c>
       <c r="C61" s="35" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D61" s="36">
-        <v>1.92</v>
+        <v>2140</v>
       </c>
       <c r="E61" s="36">
-        <v>177.7</v>
+        <v>6.1</v>
       </c>
       <c r="F61" s="36">
         <f>+E61*D61</f>
-        <v>341.18399999999997</v>
+        <v>13054</v>
       </c>
       <c r="G61" s="37">
-        <f>I61+K61</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H61" s="38">
-        <f>J61+L61</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I61" s="37">
@@ -3764,12 +3782,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A62" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62" s="40" t="s">
         <v>85</v>
-      </c>
-      <c r="B62" s="40" t="s">
-        <v>86</v>
       </c>
       <c r="C62" s="41">
         <v>0</v>
@@ -3791,27 +3809,27 @@
         <v>1</v>
       </c>
       <c r="B63" s="34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D63" s="36">
-        <v>0.23</v>
+        <v>1580</v>
       </c>
       <c r="E63" s="36">
-        <v>803.44180000000006</v>
+        <v>1.1894</v>
       </c>
       <c r="F63" s="36">
         <f>+E63*D63</f>
-        <v>184.79161400000001</v>
+        <v>1879.252</v>
       </c>
       <c r="G63" s="37">
-        <f t="shared" ref="G63:H65" si="10">I63+K63</f>
+        <f>I63+K63</f>
         <v>0</v>
       </c>
       <c r="H63" s="38">
-        <f t="shared" si="10"/>
+        <f>J63+L63</f>
         <v>0</v>
       </c>
       <c r="I63" s="37">
@@ -3829,75 +3847,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="33">
-        <v>2</v>
-      </c>
-      <c r="B64" s="34" t="s">
+    <row r="64" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B64" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="35" t="s">
+      <c r="C64" s="41">
+        <v>0</v>
+      </c>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="43"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="43"/>
+      <c r="J64" s="44"/>
+      <c r="K64" s="43"/>
+      <c r="L64" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="33">
+        <v>1</v>
+      </c>
+      <c r="B65" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="D64" s="36">
-        <v>9.6</v>
-      </c>
-      <c r="E64" s="36">
-        <v>19.7758</v>
-      </c>
-      <c r="F64" s="36">
-        <f>+E64*D64</f>
-        <v>189.84768</v>
-      </c>
-      <c r="G64" s="37">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="38">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="37">
-        <f>J64/F64</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="38">
-        <v>0</v>
-      </c>
-      <c r="K64" s="37">
-        <f>L64/F64</f>
-        <v>0</v>
-      </c>
-      <c r="L64" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="33">
-        <v>3</v>
-      </c>
-      <c r="B65" s="34" t="s">
-        <v>33</v>
-      </c>
       <c r="C65" s="35" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D65" s="36">
-        <v>12.8</v>
+        <v>1.92</v>
       </c>
       <c r="E65" s="36">
-        <v>14.3188</v>
+        <v>177.7</v>
       </c>
       <c r="F65" s="36">
         <f>+E65*D65</f>
-        <v>183.28064000000001</v>
+        <v>341.18399999999997</v>
       </c>
       <c r="G65" s="37">
-        <f t="shared" si="10"/>
+        <f>I65+K65</f>
         <v>0</v>
       </c>
       <c r="H65" s="38">
-        <f t="shared" si="10"/>
+        <f>J65+L65</f>
         <v>0</v>
       </c>
       <c r="I65" s="37">
@@ -3942,27 +3939,27 @@
         <v>1</v>
       </c>
       <c r="B67" s="34" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C67" s="35" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D67" s="36">
-        <v>33.200000000000003</v>
+        <v>0.23</v>
       </c>
       <c r="E67" s="36">
-        <v>10.320399999999999</v>
+        <v>803.44180000000006</v>
       </c>
       <c r="F67" s="36">
         <f>+E67*D67</f>
-        <v>342.63728000000003</v>
+        <v>184.79161400000001</v>
       </c>
       <c r="G67" s="37">
-        <f>I67+K67</f>
+        <f t="shared" ref="G67:H69" si="11">I67+K67</f>
         <v>0</v>
       </c>
       <c r="H67" s="38">
-        <f>J67+L67</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I67" s="37">
@@ -3985,27 +3982,27 @@
         <v>2</v>
       </c>
       <c r="B68" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D68" s="36">
-        <v>33.200000000000003</v>
+        <v>9.6</v>
       </c>
       <c r="E68" s="36">
-        <v>4.9857999999999993</v>
+        <v>19.7758</v>
       </c>
       <c r="F68" s="36">
         <f>+E68*D68</f>
-        <v>165.52856</v>
+        <v>189.84768</v>
       </c>
       <c r="G68" s="37">
-        <f>I68+K68</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H68" s="38">
-        <f>J68+L68</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I68" s="37">
@@ -4024,96 +4021,96 @@
       </c>
     </row>
     <row r="69" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="B69" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="C69" s="41">
-        <v>0</v>
-      </c>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="43"/>
-      <c r="H69" s="44"/>
-      <c r="I69" s="43"/>
-      <c r="J69" s="44"/>
-      <c r="K69" s="43"/>
-      <c r="L69" s="44">
+      <c r="A69" s="33">
+        <v>3</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69" s="36">
+        <v>12.8</v>
+      </c>
+      <c r="E69" s="36">
+        <v>14.3188</v>
+      </c>
+      <c r="F69" s="36">
+        <f>+E69*D69</f>
+        <v>183.28064000000001</v>
+      </c>
+      <c r="G69" s="37">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H69" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I69" s="37">
+        <f>J69/F69</f>
+        <v>0</v>
+      </c>
+      <c r="J69" s="38">
+        <v>0</v>
+      </c>
+      <c r="K69" s="37">
+        <f>L69/F69</f>
+        <v>0</v>
+      </c>
+      <c r="L69" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="33">
-        <v>1</v>
-      </c>
-      <c r="B70" s="34" t="s">
+      <c r="A70" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C70" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D70" s="36">
-        <v>13.86</v>
-      </c>
-      <c r="E70" s="36">
-        <v>36.616</v>
-      </c>
-      <c r="F70" s="36">
-        <f>+E70*D70</f>
-        <v>507.49775999999997</v>
-      </c>
-      <c r="G70" s="37">
-        <f t="shared" ref="G70:H74" si="11">I70+K70</f>
-        <v>0</v>
-      </c>
-      <c r="H70" s="38">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="37">
-        <f>J70/F70</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="38">
-        <v>0</v>
-      </c>
-      <c r="K70" s="37">
-        <f>L70/F70</f>
-        <v>0</v>
-      </c>
-      <c r="L70" s="38">
+      <c r="B70" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="C70" s="41">
+        <v>0</v>
+      </c>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="43"/>
+      <c r="H70" s="44"/>
+      <c r="I70" s="43"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="43"/>
+      <c r="L70" s="44">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A71" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B71" s="34" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="C71" s="35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D71" s="36">
-        <v>52.67</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="E71" s="36">
-        <v>126.7636</v>
+        <v>10.320399999999999</v>
       </c>
       <c r="F71" s="36">
         <f>+E71*D71</f>
-        <v>6676.6388120000001</v>
+        <v>342.63728000000003</v>
       </c>
       <c r="G71" s="37">
-        <f t="shared" si="11"/>
+        <f>I71+K71</f>
         <v>0</v>
       </c>
       <c r="H71" s="38">
-        <f t="shared" si="11"/>
+        <f>J71+L71</f>
         <v>0</v>
       </c>
       <c r="I71" s="37">
@@ -4133,30 +4130,30 @@
     </row>
     <row r="72" spans="1:12" s="45" customFormat="1" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B72" s="34" t="s">
         <v>97</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D72" s="36">
-        <v>127.2</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="E72" s="36">
-        <v>52.936000000000007</v>
+        <v>4.9857999999999993</v>
       </c>
       <c r="F72" s="36">
         <f>+E72*D72</f>
-        <v>6733.4592000000011</v>
+        <v>165.52856</v>
       </c>
       <c r="G72" s="37">
-        <f t="shared" si="11"/>
+        <f>I72+K72</f>
         <v>0</v>
       </c>
       <c r="H72" s="38">
-        <f t="shared" si="11"/>
+        <f>J72+L72</f>
         <v>0</v>
       </c>
       <c r="I72" s="37">
@@ -4174,75 +4171,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="33">
-        <v>4</v>
-      </c>
-      <c r="B73" s="34" t="s">
+    <row r="73" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="C73" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D73" s="36">
-        <v>127.2</v>
-      </c>
-      <c r="E73" s="36">
-        <v>10.8202</v>
-      </c>
-      <c r="F73" s="36">
-        <f>+E73*D73</f>
-        <v>1376.32944</v>
-      </c>
-      <c r="G73" s="37">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="38">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="37">
-        <f>J73/F73</f>
-        <v>0</v>
-      </c>
-      <c r="J73" s="38">
-        <v>0</v>
-      </c>
-      <c r="K73" s="37">
-        <f>L73/F73</f>
-        <v>0</v>
-      </c>
-      <c r="L73" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C73" s="41">
+        <v>0</v>
+      </c>
+      <c r="D73" s="42"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="42"/>
+      <c r="G73" s="43"/>
+      <c r="H73" s="44"/>
+      <c r="I73" s="43"/>
+      <c r="J73" s="44"/>
+      <c r="K73" s="43"/>
+      <c r="L73" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A74" s="33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D74" s="36">
-        <v>156.9</v>
+        <v>13.86</v>
       </c>
       <c r="E74" s="36">
-        <v>3.67</v>
+        <v>36.616</v>
       </c>
       <c r="F74" s="36">
         <f>+E74*D74</f>
-        <v>575.82299999999998</v>
+        <v>507.49775999999997</v>
       </c>
       <c r="G74" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="G74:H78" si="12">I74+K74</f>
         <v>0</v>
       </c>
       <c r="H74" s="38">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I74" s="37">
@@ -4261,107 +4237,128 @@
       </c>
     </row>
     <row r="75" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="B75" s="40" t="s">
+      <c r="A75" s="33">
+        <v>2</v>
+      </c>
+      <c r="B75" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="C75" s="41">
-        <v>0</v>
-      </c>
-      <c r="D75" s="42"/>
-      <c r="E75" s="42"/>
-      <c r="F75" s="42"/>
-      <c r="G75" s="43"/>
-      <c r="H75" s="44"/>
-      <c r="I75" s="43"/>
-      <c r="J75" s="44"/>
-      <c r="K75" s="43"/>
-      <c r="L75" s="44">
+      <c r="C75" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D75" s="36">
+        <v>52.67</v>
+      </c>
+      <c r="E75" s="36">
+        <v>126.7636</v>
+      </c>
+      <c r="F75" s="36">
+        <f>+E75*D75</f>
+        <v>6676.6388120000001</v>
+      </c>
+      <c r="G75" s="37">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="H75" s="38">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I75" s="37">
+        <f>J75/F75</f>
+        <v>0</v>
+      </c>
+      <c r="J75" s="38">
+        <v>0</v>
+      </c>
+      <c r="K75" s="37">
+        <f>L75/F75</f>
+        <v>0</v>
+      </c>
+      <c r="L75" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A76" s="33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B76" s="34" t="s">
         <v>102</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D76" s="36">
-        <v>26.84</v>
+        <v>127.2</v>
       </c>
       <c r="E76" s="36">
-        <v>281.11200000000002</v>
+        <v>52.936000000000007</v>
       </c>
       <c r="F76" s="36">
-        <f t="shared" ref="F76:F81" si="12">+E76*D76</f>
-        <v>7545.046080000001</v>
+        <f>+E76*D76</f>
+        <v>6733.4592000000011</v>
       </c>
       <c r="G76" s="37">
-        <f t="shared" ref="G76:H81" si="13">I76+K76</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H76" s="38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I76" s="37">
-        <f t="shared" ref="I76:I81" si="14">J76/F76</f>
+        <f>J76/F76</f>
         <v>0</v>
       </c>
       <c r="J76" s="38">
         <v>0</v>
       </c>
       <c r="K76" s="37">
-        <f t="shared" ref="K76:K81" si="15">L76/F76</f>
+        <f>L76/F76</f>
         <v>0</v>
       </c>
       <c r="L76" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A77" s="33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B77" s="34" t="s">
         <v>103</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D77" s="36">
-        <v>17.84</v>
+        <v>127.2</v>
       </c>
       <c r="E77" s="36">
-        <v>381.23320000000001</v>
+        <v>10.8202</v>
       </c>
       <c r="F77" s="36">
+        <f>+E77*D77</f>
+        <v>1376.32944</v>
+      </c>
+      <c r="G77" s="37">
         <f t="shared" si="12"/>
-        <v>6801.200288</v>
-      </c>
-      <c r="G77" s="37">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H77" s="38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I77" s="37">
-        <f t="shared" si="14"/>
+        <f>J77/F77</f>
         <v>0</v>
       </c>
       <c r="J77" s="38">
         <v>0</v>
       </c>
       <c r="K77" s="37">
-        <f t="shared" si="15"/>
+        <f>L77/F77</f>
         <v>0</v>
       </c>
       <c r="L77" s="38">
@@ -4370,41 +4367,41 @@
     </row>
     <row r="78" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A78" s="33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B78" s="34" t="s">
         <v>104</v>
       </c>
       <c r="C78" s="35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D78" s="36">
-        <v>27.58</v>
+        <v>156.9</v>
       </c>
       <c r="E78" s="36">
-        <v>280</v>
+        <v>3.67</v>
       </c>
       <c r="F78" s="36">
+        <f>+E78*D78</f>
+        <v>575.82299999999998</v>
+      </c>
+      <c r="G78" s="37">
         <f t="shared" si="12"/>
-        <v>7722.4</v>
-      </c>
-      <c r="G78" s="37">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H78" s="38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I78" s="37">
-        <f t="shared" si="14"/>
+        <f>J78/F78</f>
         <v>0</v>
       </c>
       <c r="J78" s="38">
         <v>0</v>
       </c>
       <c r="K78" s="37">
-        <f t="shared" si="15"/>
+        <f>L78/F78</f>
         <v>0</v>
       </c>
       <c r="L78" s="38">
@@ -4412,279 +4409,279 @@
       </c>
     </row>
     <row r="79" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="33">
-        <v>4</v>
-      </c>
-      <c r="B79" s="34" t="s">
+      <c r="A79" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="C79" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D79" s="36">
-        <v>0.25600000000000001</v>
-      </c>
-      <c r="E79" s="36">
-        <v>249.38800000000001</v>
-      </c>
-      <c r="F79" s="36">
-        <f t="shared" si="12"/>
-        <v>63.843328</v>
-      </c>
-      <c r="G79" s="37">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H79" s="38">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="37">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="J79" s="38">
-        <v>0</v>
-      </c>
-      <c r="K79" s="37">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="L79" s="38">
+      <c r="B79" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="C79" s="41">
+        <v>0</v>
+      </c>
+      <c r="D79" s="42"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="42"/>
+      <c r="G79" s="43"/>
+      <c r="H79" s="44"/>
+      <c r="I79" s="43"/>
+      <c r="J79" s="44"/>
+      <c r="K79" s="43"/>
+      <c r="L79" s="44">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:12" s="45" customFormat="1" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D80" s="36">
-        <v>23.52</v>
+        <v>26.84</v>
       </c>
       <c r="E80" s="36">
-        <v>30.802</v>
+        <v>281.11200000000002</v>
       </c>
       <c r="F80" s="36">
-        <f t="shared" si="12"/>
-        <v>724.46303999999998</v>
+        <f t="shared" ref="F80:F85" si="13">+E80*D80</f>
+        <v>7545.046080000001</v>
       </c>
       <c r="G80" s="37">
+        <f t="shared" ref="G80:H85" si="14">I80+K80</f>
+        <v>0</v>
+      </c>
+      <c r="H80" s="38">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I80" s="37">
+        <f t="shared" ref="I80:I85" si="15">J80/F80</f>
+        <v>0</v>
+      </c>
+      <c r="J80" s="38">
+        <v>0</v>
+      </c>
+      <c r="K80" s="37">
+        <f t="shared" ref="K80:K85" si="16">L80/F80</f>
+        <v>0</v>
+      </c>
+      <c r="L80" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="33">
+        <v>2</v>
+      </c>
+      <c r="B81" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C81" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D81" s="36">
+        <v>17.84</v>
+      </c>
+      <c r="E81" s="36">
+        <v>381.23320000000001</v>
+      </c>
+      <c r="F81" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H80" s="38">
+        <v>6801.200288</v>
+      </c>
+      <c r="G81" s="37">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H81" s="38">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I81" s="37">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J81" s="38">
+        <v>0</v>
+      </c>
+      <c r="K81" s="37">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L81" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="33">
+        <v>3</v>
+      </c>
+      <c r="B82" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C82" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D82" s="36">
+        <v>27.58</v>
+      </c>
+      <c r="E82" s="36">
+        <v>280</v>
+      </c>
+      <c r="F82" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="37">
+        <v>7722.4</v>
+      </c>
+      <c r="G82" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J80" s="38">
-        <v>0</v>
-      </c>
-      <c r="K80" s="37">
+      <c r="H82" s="38">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I82" s="37">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L80" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="33">
-        <v>6</v>
-      </c>
-      <c r="B81" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="C81" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D81" s="36">
-        <v>24.44</v>
-      </c>
-      <c r="E81" s="36">
-        <v>41.92</v>
-      </c>
-      <c r="F81" s="36">
-        <f t="shared" si="12"/>
-        <v>1024.5248000000001</v>
-      </c>
-      <c r="G81" s="37">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H81" s="38">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="I81" s="37">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="J81" s="38">
-        <v>0</v>
-      </c>
-      <c r="K81" s="37">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="L81" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="B82" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C82" s="41">
-        <v>0</v>
-      </c>
-      <c r="D82" s="42"/>
-      <c r="E82" s="42"/>
-      <c r="F82" s="42"/>
-      <c r="G82" s="43"/>
-      <c r="H82" s="44"/>
-      <c r="I82" s="43"/>
-      <c r="J82" s="44"/>
-      <c r="K82" s="43"/>
-      <c r="L82" s="44">
+      <c r="J82" s="38">
+        <v>0</v>
+      </c>
+      <c r="K82" s="37">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L82" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A83" s="33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B83" s="34" t="s">
         <v>110</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D83" s="36">
-        <v>16.3</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="E83" s="36">
-        <v>9.0555999999999983</v>
+        <v>249.38800000000001</v>
       </c>
       <c r="F83" s="36">
-        <f>+E83*D83</f>
-        <v>147.60627999999997</v>
+        <f t="shared" si="13"/>
+        <v>63.843328</v>
       </c>
       <c r="G83" s="37">
-        <f t="shared" ref="G83:H85" si="16">I83+K83</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H83" s="38">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I83" s="37">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J83" s="38">
+        <v>0</v>
+      </c>
+      <c r="K83" s="37">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I83" s="37">
-        <f>J83/F83</f>
-        <v>0</v>
-      </c>
-      <c r="J83" s="38">
-        <v>0</v>
-      </c>
-      <c r="K83" s="37">
-        <f>L83/F83</f>
-        <v>0</v>
-      </c>
       <c r="L83" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A84" s="33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B84" s="34" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="C84" s="35" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D84" s="36">
-        <v>16.3</v>
+        <v>23.52</v>
       </c>
       <c r="E84" s="36">
-        <v>3.6884000000000001</v>
+        <v>30.802</v>
       </c>
       <c r="F84" s="36">
-        <f>+E84*D84</f>
-        <v>60.120920000000005</v>
+        <f t="shared" si="13"/>
+        <v>724.46303999999998</v>
       </c>
       <c r="G84" s="37">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H84" s="38">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I84" s="37">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J84" s="38">
+        <v>0</v>
+      </c>
+      <c r="K84" s="37">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H84" s="38">
+      <c r="L84" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="33">
+        <v>6</v>
+      </c>
+      <c r="B85" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="C85" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D85" s="36">
+        <v>24.44</v>
+      </c>
+      <c r="E85" s="36">
+        <v>41.92</v>
+      </c>
+      <c r="F85" s="36">
+        <f t="shared" si="13"/>
+        <v>1024.5248000000001</v>
+      </c>
+      <c r="G85" s="37">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="38">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I85" s="37">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J85" s="38">
+        <v>0</v>
+      </c>
+      <c r="K85" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I84" s="37">
-        <f>J84/F84</f>
-        <v>0</v>
-      </c>
-      <c r="J84" s="38">
-        <v>0</v>
-      </c>
-      <c r="K84" s="37">
-        <f>L84/F84</f>
-        <v>0</v>
-      </c>
-      <c r="L84" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="33">
-        <v>3</v>
-      </c>
-      <c r="B85" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="C85" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D85" s="36">
-        <v>1.08</v>
-      </c>
-      <c r="E85" s="36">
-        <v>114.1564</v>
-      </c>
-      <c r="F85" s="36">
-        <f>+E85*D85</f>
-        <v>123.28891200000001</v>
-      </c>
-      <c r="G85" s="37">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H85" s="38">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I85" s="37">
-        <f>J85/F85</f>
-        <v>0</v>
-      </c>
-      <c r="J85" s="38">
-        <v>0</v>
-      </c>
-      <c r="K85" s="37">
-        <f>L85/F85</f>
         <v>0</v>
       </c>
       <c r="L85" s="38">
@@ -4693,10 +4690,10 @@
     </row>
     <row r="86" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A86" s="31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C86" s="41">
         <v>0</v>
@@ -4713,28 +4710,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A87" s="33">
         <v>1</v>
       </c>
       <c r="B87" s="34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C87" s="35" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="D87" s="36">
-        <v>12</v>
+        <v>16.3</v>
       </c>
       <c r="E87" s="36">
-        <v>18.784400000000002</v>
+        <v>9.0555999999999983</v>
       </c>
       <c r="F87" s="36">
         <f>+E87*D87</f>
-        <v>225.4128</v>
+        <v>147.60627999999997</v>
       </c>
       <c r="G87" s="37">
-        <f t="shared" ref="G87:H91" si="17">I87+K87</f>
+        <f t="shared" ref="G87:H89" si="17">I87+K87</f>
         <v>0</v>
       </c>
       <c r="H87" s="38">
@@ -4756,25 +4753,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A88" s="33">
         <v>2</v>
       </c>
       <c r="B88" s="34" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="C88" s="35" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="D88" s="36">
-        <v>12</v>
+        <v>16.3</v>
       </c>
       <c r="E88" s="36">
-        <v>27.2014</v>
+        <v>3.6884000000000001</v>
       </c>
       <c r="F88" s="36">
         <f>+E88*D88</f>
-        <v>326.41679999999997</v>
+        <v>60.120920000000005</v>
       </c>
       <c r="G88" s="37">
         <f t="shared" si="17"/>
@@ -4799,25 +4796,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A89" s="33">
         <v>3</v>
       </c>
       <c r="B89" s="34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C89" s="35" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="D89" s="36">
-        <v>5</v>
+        <v>1.08</v>
       </c>
       <c r="E89" s="36">
-        <v>22.905200000000001</v>
+        <v>114.1564</v>
       </c>
       <c r="F89" s="36">
         <f>+E89*D89</f>
-        <v>114.52600000000001</v>
+        <v>123.28891200000001</v>
       </c>
       <c r="G89" s="37">
         <f t="shared" si="17"/>
@@ -4842,75 +4839,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="33">
-        <v>4</v>
-      </c>
-      <c r="B90" s="34" t="s">
+    <row r="90" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B90" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="C90" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D90" s="36">
-        <v>5</v>
-      </c>
-      <c r="E90" s="36">
-        <v>11.779</v>
-      </c>
-      <c r="F90" s="36">
-        <f>+E90*D90</f>
-        <v>58.894999999999996</v>
-      </c>
-      <c r="G90" s="37">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="H90" s="38">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="I90" s="37">
-        <f>J90/F90</f>
-        <v>0</v>
-      </c>
-      <c r="J90" s="38">
-        <v>0</v>
-      </c>
-      <c r="K90" s="37">
-        <f>L90/F90</f>
-        <v>0</v>
-      </c>
-      <c r="L90" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C90" s="41">
+        <v>0</v>
+      </c>
+      <c r="D90" s="42"/>
+      <c r="E90" s="42"/>
+      <c r="F90" s="42"/>
+      <c r="G90" s="43"/>
+      <c r="H90" s="44"/>
+      <c r="I90" s="43"/>
+      <c r="J90" s="44"/>
+      <c r="K90" s="43"/>
+      <c r="L90" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A91" s="33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B91" s="34" t="s">
         <v>119</v>
       </c>
       <c r="C91" s="35" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D91" s="36">
         <v>12</v>
       </c>
       <c r="E91" s="36">
-        <v>2.6785999999999999</v>
+        <v>18.784400000000002</v>
       </c>
       <c r="F91" s="36">
         <f>+E91*D91</f>
-        <v>32.1432</v>
+        <v>225.4128</v>
       </c>
       <c r="G91" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="G91:H95" si="18">I91+K91</f>
         <v>0</v>
       </c>
       <c r="H91" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I91" s="37">
@@ -4928,54 +4904,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="31" t="s">
+    <row r="92" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="33">
+        <v>2</v>
+      </c>
+      <c r="B92" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="C92" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="B92" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C92" s="41">
-        <v>0</v>
-      </c>
-      <c r="D92" s="42"/>
-      <c r="E92" s="42"/>
-      <c r="F92" s="42"/>
-      <c r="G92" s="43"/>
-      <c r="H92" s="44"/>
-      <c r="I92" s="43"/>
-      <c r="J92" s="44"/>
-      <c r="K92" s="43"/>
-      <c r="L92" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="D92" s="36">
+        <v>12</v>
+      </c>
+      <c r="E92" s="36">
+        <v>27.2014</v>
+      </c>
+      <c r="F92" s="36">
+        <f>+E92*D92</f>
+        <v>326.41679999999997</v>
+      </c>
+      <c r="G92" s="37">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="H92" s="38">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="I92" s="37">
+        <f>J92/F92</f>
+        <v>0</v>
+      </c>
+      <c r="J92" s="38">
+        <v>0</v>
+      </c>
+      <c r="K92" s="37">
+        <f>L92/F92</f>
+        <v>0</v>
+      </c>
+      <c r="L92" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A93" s="33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B93" s="34" t="s">
         <v>122</v>
       </c>
       <c r="C93" s="35" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="D93" s="36">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="E93" s="36">
-        <v>111.1066</v>
+        <v>22.905200000000001</v>
       </c>
       <c r="F93" s="36">
         <f>+E93*D93</f>
-        <v>338.87512999999996</v>
+        <v>114.52600000000001</v>
       </c>
       <c r="G93" s="37">
-        <f>I93+K93</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H93" s="38">
-        <f>J93+L93</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I93" s="37">
@@ -4993,54 +4990,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="31" t="s">
+    <row r="94" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="33">
+        <v>4</v>
+      </c>
+      <c r="B94" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="B94" s="40" t="s">
+      <c r="C94" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="D94" s="36">
+        <v>5</v>
+      </c>
+      <c r="E94" s="36">
+        <v>11.779</v>
+      </c>
+      <c r="F94" s="36">
+        <f>+E94*D94</f>
+        <v>58.894999999999996</v>
+      </c>
+      <c r="G94" s="37">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="H94" s="38">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="I94" s="37">
+        <f>J94/F94</f>
+        <v>0</v>
+      </c>
+      <c r="J94" s="38">
+        <v>0</v>
+      </c>
+      <c r="K94" s="37">
+        <f>L94/F94</f>
+        <v>0</v>
+      </c>
+      <c r="L94" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="33">
+        <v>5</v>
+      </c>
+      <c r="B95" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="C94" s="41">
-        <v>0</v>
-      </c>
-      <c r="D94" s="42"/>
-      <c r="E94" s="42"/>
-      <c r="F94" s="42"/>
-      <c r="G94" s="43"/>
-      <c r="H94" s="44"/>
-      <c r="I94" s="43"/>
-      <c r="J94" s="44"/>
-      <c r="K94" s="43"/>
-      <c r="L94" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="33">
-        <v>1</v>
-      </c>
-      <c r="B95" s="34" t="s">
-        <v>104</v>
-      </c>
       <c r="C95" s="35" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="D95" s="36">
-        <v>4.2300000000000004</v>
+        <v>12</v>
       </c>
       <c r="E95" s="36">
-        <v>280</v>
+        <v>2.6785999999999999</v>
       </c>
       <c r="F95" s="36">
         <f>+E95*D95</f>
-        <v>1184.4000000000001</v>
+        <v>32.1432</v>
       </c>
       <c r="G95" s="37">
-        <f>I95+K95</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H95" s="38">
-        <f>J95+L95</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I95" s="37">
@@ -5085,20 +5103,20 @@
         <v>1</v>
       </c>
       <c r="B97" s="34" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="C97" s="35" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D97" s="36">
-        <v>1.2589999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="E97" s="36">
-        <v>803.86</v>
+        <v>111.1066</v>
       </c>
       <c r="F97" s="36">
         <f>+E97*D97</f>
-        <v>1012.0597399999999</v>
+        <v>338.87512999999996</v>
       </c>
       <c r="G97" s="37">
         <f>I97+K97</f>
@@ -5125,10 +5143,10 @@
     </row>
     <row r="98" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A98" s="31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B98" s="40" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C98" s="41">
         <v>0</v>
@@ -5150,20 +5168,20 @@
         <v>1</v>
       </c>
       <c r="B99" s="34" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C99" s="35" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D99" s="36">
-        <v>2.16</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="E99" s="36">
-        <v>157.88380000000001</v>
+        <v>280</v>
       </c>
       <c r="F99" s="36">
         <f>+E99*D99</f>
-        <v>341.02900800000003</v>
+        <v>1184.4000000000001</v>
       </c>
       <c r="G99" s="37">
         <f>I99+K99</f>
@@ -5210,32 +5228,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:12" s="45" customFormat="1" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" s="45" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="33">
         <v>1</v>
       </c>
       <c r="B101" s="34" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="C101" s="35" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D101" s="36">
-        <v>20.16</v>
+        <v>1.2589999999999999</v>
       </c>
       <c r="E101" s="36">
-        <v>6.5157999999999996</v>
+        <v>803.86</v>
       </c>
       <c r="F101" s="36">
         <f>+E101*D101</f>
-        <v>131.35852800000001</v>
+        <v>1012.0597399999999</v>
       </c>
       <c r="G101" s="37">
-        <f t="shared" ref="G101:H104" si="18">I101+K101</f>
+        <f>I101+K101</f>
         <v>0</v>
       </c>
       <c r="H101" s="38">
-        <f t="shared" si="18"/>
+        <f>J101+L101</f>
         <v>0</v>
       </c>
       <c r="I101" s="37">
@@ -5253,75 +5271,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="33">
-        <v>2</v>
-      </c>
-      <c r="B102" s="34" t="s">
+    <row r="102" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="B102" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="C102" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D102" s="36">
-        <v>20.16</v>
-      </c>
-      <c r="E102" s="36">
-        <v>8.2498000000000005</v>
-      </c>
-      <c r="F102" s="36">
-        <f>+E102*D102</f>
-        <v>166.315968</v>
-      </c>
-      <c r="G102" s="37">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H102" s="38">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="I102" s="37">
-        <f>J102/F102</f>
-        <v>0</v>
-      </c>
-      <c r="J102" s="38">
-        <v>0</v>
-      </c>
-      <c r="K102" s="37">
-        <f>L102/F102</f>
-        <v>0</v>
-      </c>
-      <c r="L102" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C102" s="41">
+        <v>0</v>
+      </c>
+      <c r="D102" s="42"/>
+      <c r="E102" s="42"/>
+      <c r="F102" s="42"/>
+      <c r="G102" s="43"/>
+      <c r="H102" s="44"/>
+      <c r="I102" s="43"/>
+      <c r="J102" s="44"/>
+      <c r="K102" s="43"/>
+      <c r="L102" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A103" s="33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B103" s="34" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="C103" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D103" s="36">
-        <v>85</v>
+        <v>2.16</v>
       </c>
       <c r="E103" s="36">
-        <v>10.320399999999999</v>
+        <v>157.88380000000001</v>
       </c>
       <c r="F103" s="36">
         <f>+E103*D103</f>
-        <v>877.23399999999992</v>
+        <v>341.02900800000003</v>
       </c>
       <c r="G103" s="37">
-        <f t="shared" si="18"/>
+        <f>I103+K103</f>
         <v>0</v>
       </c>
       <c r="H103" s="38">
-        <f t="shared" si="18"/>
+        <f>J103+L103</f>
         <v>0</v>
       </c>
       <c r="I103" s="37">
@@ -5339,32 +5336,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A104" s="33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B104" s="34" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="C104" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D104" s="36">
-        <v>85</v>
+        <v>2.16</v>
       </c>
       <c r="E104" s="36">
-        <v>4.9857999999999993</v>
+        <v>178.6</v>
       </c>
       <c r="F104" s="36">
         <f>+E104*D104</f>
-        <v>423.79299999999995</v>
+        <v>385.77600000000001</v>
       </c>
       <c r="G104" s="37">
-        <f t="shared" si="18"/>
+        <f>I104+K104</f>
         <v>0</v>
       </c>
       <c r="H104" s="38">
-        <f t="shared" si="18"/>
+        <f>J104+L104</f>
         <v>0</v>
       </c>
       <c r="I104" s="37">
@@ -5384,10 +5381,10 @@
     </row>
     <row r="105" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A105" s="31" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B105" s="40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C105" s="41">
         <v>0</v>
@@ -5409,27 +5406,27 @@
         <v>1</v>
       </c>
       <c r="B106" s="34" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="C106" s="35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D106" s="36">
-        <v>4.13</v>
+        <v>20.16</v>
       </c>
       <c r="E106" s="36">
-        <v>280</v>
+        <v>6.5157999999999996</v>
       </c>
       <c r="F106" s="36">
         <f>+E106*D106</f>
-        <v>1156.3999999999999</v>
+        <v>131.35852800000001</v>
       </c>
       <c r="G106" s="37">
-        <f>I106+K106</f>
+        <f t="shared" ref="G106:H109" si="19">I106+K106</f>
         <v>0</v>
       </c>
       <c r="H106" s="38">
-        <f>J106+L106</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I106" s="37">
@@ -5447,54 +5444,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="B107" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="C107" s="41">
-        <v>0</v>
-      </c>
-      <c r="D107" s="42"/>
-      <c r="E107" s="42"/>
-      <c r="F107" s="42"/>
-      <c r="G107" s="43"/>
-      <c r="H107" s="44"/>
-      <c r="I107" s="43"/>
-      <c r="J107" s="44"/>
-      <c r="K107" s="43"/>
-      <c r="L107" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="33">
+        <v>2</v>
+      </c>
+      <c r="B107" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="C107" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D107" s="36">
+        <v>20.16</v>
+      </c>
+      <c r="E107" s="36">
+        <v>8.2498000000000005</v>
+      </c>
+      <c r="F107" s="36">
+        <f>+E107*D107</f>
+        <v>166.315968</v>
+      </c>
+      <c r="G107" s="37">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H107" s="38">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="I107" s="37">
+        <f>J107/F107</f>
+        <v>0</v>
+      </c>
+      <c r="J107" s="38">
+        <v>0</v>
+      </c>
+      <c r="K107" s="37">
+        <f>L107/F107</f>
+        <v>0</v>
+      </c>
+      <c r="L107" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A108" s="33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B108" s="34" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="C108" s="35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D108" s="36">
-        <v>4.13</v>
+        <v>85</v>
       </c>
       <c r="E108" s="36">
-        <v>280</v>
+        <v>10.320399999999999</v>
       </c>
       <c r="F108" s="36">
         <f>+E108*D108</f>
-        <v>1156.3999999999999</v>
+        <v>877.23399999999992</v>
       </c>
       <c r="G108" s="37">
-        <f>I108+K108</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H108" s="38">
-        <f>J108+L108</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I108" s="37">
@@ -5512,97 +5530,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="B109" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="C109" s="41">
-        <v>0</v>
-      </c>
-      <c r="D109" s="42"/>
-      <c r="E109" s="42"/>
-      <c r="F109" s="42"/>
-      <c r="G109" s="43"/>
-      <c r="H109" s="44"/>
-      <c r="I109" s="43"/>
-      <c r="J109" s="44"/>
-      <c r="K109" s="43"/>
-      <c r="L109" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="33">
-        <v>1</v>
-      </c>
-      <c r="B110" s="34" t="s">
+    <row r="109" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="33">
+        <v>4</v>
+      </c>
+      <c r="B109" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C109" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D109" s="36">
+        <v>85</v>
+      </c>
+      <c r="E109" s="36">
+        <v>4.9857999999999993</v>
+      </c>
+      <c r="F109" s="36">
+        <f>+E109*D109</f>
+        <v>423.79299999999995</v>
+      </c>
+      <c r="G109" s="37">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H109" s="38">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="I109" s="37">
+        <f>J109/F109</f>
+        <v>0</v>
+      </c>
+      <c r="J109" s="38">
+        <v>0</v>
+      </c>
+      <c r="K109" s="37">
+        <f>L109/F109</f>
+        <v>0</v>
+      </c>
+      <c r="L109" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="C110" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D110" s="36">
-        <v>14.49</v>
-      </c>
-      <c r="E110" s="36">
-        <v>212.52520000000001</v>
-      </c>
-      <c r="F110" s="36">
-        <f>+E110*D110</f>
-        <v>3079.4901480000003</v>
-      </c>
-      <c r="G110" s="37">
-        <f t="shared" ref="G110:H112" si="19">I110+K110</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="38">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I110" s="37">
-        <f>J110/F110</f>
-        <v>0</v>
-      </c>
-      <c r="J110" s="38">
-        <v>0</v>
-      </c>
-      <c r="K110" s="37">
-        <f>L110/F110</f>
-        <v>0</v>
-      </c>
-      <c r="L110" s="38">
+      <c r="B110" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="C110" s="41">
+        <v>0</v>
+      </c>
+      <c r="D110" s="42"/>
+      <c r="E110" s="42"/>
+      <c r="F110" s="42"/>
+      <c r="G110" s="43"/>
+      <c r="H110" s="44"/>
+      <c r="I110" s="43"/>
+      <c r="J110" s="44"/>
+      <c r="K110" s="43"/>
+      <c r="L110" s="44">
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A111" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B111" s="34" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C111" s="35" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D111" s="36">
-        <v>1.58</v>
+        <v>4.13</v>
       </c>
       <c r="E111" s="36">
         <v>280</v>
       </c>
       <c r="F111" s="36">
         <f>+E111*D111</f>
-        <v>442.40000000000003</v>
+        <v>1156.3999999999999</v>
       </c>
       <c r="G111" s="37">
-        <f t="shared" si="19"/>
+        <f>I111+K111</f>
         <v>0</v>
       </c>
       <c r="H111" s="38">
-        <f t="shared" si="19"/>
+        <f>J111+L111</f>
         <v>0</v>
       </c>
       <c r="I111" s="37">
@@ -5620,136 +5638,115 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="33">
-        <v>3</v>
-      </c>
-      <c r="B112" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="C112" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D112" s="36">
-        <v>3</v>
-      </c>
-      <c r="E112" s="36">
-        <v>29.4862</v>
-      </c>
-      <c r="F112" s="36">
-        <f>+E112*D112</f>
-        <v>88.458600000000004</v>
-      </c>
-      <c r="G112" s="37">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="H112" s="38">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I112" s="37">
-        <f>J112/F112</f>
-        <v>0</v>
-      </c>
-      <c r="J112" s="38">
-        <v>0</v>
-      </c>
-      <c r="K112" s="37">
-        <f>L112/F112</f>
-        <v>0</v>
-      </c>
-      <c r="L112" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="31" t="s">
+    <row r="112" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="B113" s="40" t="s">
+      <c r="B112" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="C113" s="41">
-        <v>0</v>
-      </c>
-      <c r="D113" s="42"/>
-      <c r="E113" s="42"/>
-      <c r="F113" s="42"/>
-      <c r="G113" s="43"/>
-      <c r="H113" s="44"/>
-      <c r="I113" s="43"/>
-      <c r="J113" s="44"/>
-      <c r="K113" s="43"/>
-      <c r="L113" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="33">
+      <c r="C112" s="41">
+        <v>0</v>
+      </c>
+      <c r="D112" s="42"/>
+      <c r="E112" s="42"/>
+      <c r="F112" s="42"/>
+      <c r="G112" s="43"/>
+      <c r="H112" s="44"/>
+      <c r="I112" s="43"/>
+      <c r="J112" s="44"/>
+      <c r="K112" s="43"/>
+      <c r="L112" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="33">
         <v>1</v>
       </c>
-      <c r="B114" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="C114" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D114" s="36">
-        <v>14.49</v>
-      </c>
-      <c r="E114" s="36">
-        <v>212.52520000000001</v>
-      </c>
-      <c r="F114" s="36">
-        <f>+E114*D114</f>
-        <v>3079.4901480000003</v>
-      </c>
-      <c r="G114" s="37">
-        <f t="shared" ref="G114:H116" si="20">I114+K114</f>
-        <v>0</v>
-      </c>
-      <c r="H114" s="38">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="I114" s="37">
-        <f>J114/F114</f>
-        <v>0</v>
-      </c>
-      <c r="J114" s="38">
-        <v>0</v>
-      </c>
-      <c r="K114" s="37">
-        <f>L114/F114</f>
-        <v>0</v>
-      </c>
-      <c r="L114" s="38">
+      <c r="B113" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C113" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D113" s="36">
+        <v>4.13</v>
+      </c>
+      <c r="E113" s="36">
+        <v>280</v>
+      </c>
+      <c r="F113" s="36">
+        <f>+E113*D113</f>
+        <v>1156.3999999999999</v>
+      </c>
+      <c r="G113" s="37">
+        <f>I113+K113</f>
+        <v>0</v>
+      </c>
+      <c r="H113" s="38">
+        <f>J113+L113</f>
+        <v>0</v>
+      </c>
+      <c r="I113" s="37">
+        <f>J113/F113</f>
+        <v>0</v>
+      </c>
+      <c r="J113" s="38">
+        <v>0</v>
+      </c>
+      <c r="K113" s="37">
+        <f>L113/F113</f>
+        <v>0</v>
+      </c>
+      <c r="L113" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="B114" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="C114" s="41">
+        <v>0</v>
+      </c>
+      <c r="D114" s="42"/>
+      <c r="E114" s="42"/>
+      <c r="F114" s="42"/>
+      <c r="G114" s="43"/>
+      <c r="H114" s="44"/>
+      <c r="I114" s="43"/>
+      <c r="J114" s="44"/>
+      <c r="K114" s="43"/>
+      <c r="L114" s="44">
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A115" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B115" s="34" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="C115" s="35" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D115" s="36">
-        <v>1.58</v>
+        <v>14.49</v>
       </c>
       <c r="E115" s="36">
-        <v>280</v>
+        <v>212.52520000000001</v>
       </c>
       <c r="F115" s="36">
         <f>+E115*D115</f>
-        <v>442.40000000000003</v>
+        <v>3079.4901480000003</v>
       </c>
       <c r="G115" s="37">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G115:H117" si="20">I115+K115</f>
         <v>0</v>
       </c>
       <c r="H115" s="38">
@@ -5773,23 +5770,23 @@
     </row>
     <row r="116" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A116" s="33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B116" s="34" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="C116" s="35" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="D116" s="36">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="E116" s="36">
-        <v>29.4862</v>
+        <v>280</v>
       </c>
       <c r="F116" s="36">
         <f>+E116*D116</f>
-        <v>88.458600000000004</v>
+        <v>442.40000000000003</v>
       </c>
       <c r="G116" s="37">
         <f t="shared" si="20"/>
@@ -5814,119 +5811,140 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:12" s="45" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="B117" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="C117" s="41">
-        <v>0</v>
-      </c>
-      <c r="D117" s="42"/>
-      <c r="E117" s="42"/>
-      <c r="F117" s="42"/>
-      <c r="G117" s="43"/>
-      <c r="H117" s="44"/>
-      <c r="I117" s="43"/>
-      <c r="J117" s="44"/>
-      <c r="K117" s="43"/>
-      <c r="L117" s="44">
+    <row r="117" spans="1:12" s="45" customFormat="1" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="33">
+        <v>3</v>
+      </c>
+      <c r="B117" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="C117" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="D117" s="36">
+        <v>3</v>
+      </c>
+      <c r="E117" s="36">
+        <v>29.4862</v>
+      </c>
+      <c r="F117" s="36">
+        <f>+E117*D117</f>
+        <v>88.458600000000004</v>
+      </c>
+      <c r="G117" s="37">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H117" s="38">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="I117" s="37">
+        <f>J117/F117</f>
+        <v>0</v>
+      </c>
+      <c r="J117" s="38">
+        <v>0</v>
+      </c>
+      <c r="K117" s="37">
+        <f>L117/F117</f>
+        <v>0</v>
+      </c>
+      <c r="L117" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="33">
+      <c r="A118" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B118" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="C118" s="41">
+        <v>0</v>
+      </c>
+      <c r="D118" s="42"/>
+      <c r="E118" s="42"/>
+      <c r="F118" s="42"/>
+      <c r="G118" s="43"/>
+      <c r="H118" s="44"/>
+      <c r="I118" s="43"/>
+      <c r="J118" s="44"/>
+      <c r="K118" s="43"/>
+      <c r="L118" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="33">
         <v>1</v>
       </c>
-      <c r="B118" s="34" t="s">
+      <c r="B119" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="C118" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D118" s="36">
-        <v>8.4600000000000009</v>
-      </c>
-      <c r="E118" s="36">
-        <v>117.2572</v>
-      </c>
-      <c r="F118" s="36">
-        <f>+E118*D118</f>
-        <v>991.99591200000009</v>
-      </c>
-      <c r="G118" s="37">
-        <f>I118+K118</f>
-        <v>0</v>
-      </c>
-      <c r="H118" s="38">
-        <f>J118+L118</f>
-        <v>0</v>
-      </c>
-      <c r="I118" s="37">
-        <f>J118/F118</f>
-        <v>0</v>
-      </c>
-      <c r="J118" s="38">
-        <v>0</v>
-      </c>
-      <c r="K118" s="37">
-        <f>L118/F118</f>
-        <v>0</v>
-      </c>
-      <c r="L118" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="B119" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="C119" s="41">
-        <v>0</v>
-      </c>
-      <c r="D119" s="42"/>
-      <c r="E119" s="42"/>
-      <c r="F119" s="42"/>
-      <c r="G119" s="43"/>
-      <c r="H119" s="44"/>
-      <c r="I119" s="43"/>
-      <c r="J119" s="44"/>
-      <c r="K119" s="43"/>
-      <c r="L119" s="44">
+      <c r="C119" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D119" s="36">
+        <v>14.49</v>
+      </c>
+      <c r="E119" s="36">
+        <v>212.52520000000001</v>
+      </c>
+      <c r="F119" s="36">
+        <f>+E119*D119</f>
+        <v>3079.4901480000003</v>
+      </c>
+      <c r="G119" s="37">
+        <f t="shared" ref="G119:H121" si="21">I119+K119</f>
+        <v>0</v>
+      </c>
+      <c r="H119" s="38">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I119" s="37">
+        <f>J119/F119</f>
+        <v>0</v>
+      </c>
+      <c r="J119" s="38">
+        <v>0</v>
+      </c>
+      <c r="K119" s="37">
+        <f>L119/F119</f>
+        <v>0</v>
+      </c>
+      <c r="L119" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A120" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B120" s="34" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="C120" s="35" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D120" s="36">
-        <v>2.91</v>
+        <v>1.58</v>
       </c>
       <c r="E120" s="36">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="F120" s="36">
         <f>+E120*D120</f>
-        <v>742.05000000000007</v>
+        <v>442.40000000000003</v>
       </c>
       <c r="G120" s="37">
-        <f>I120+K120</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H120" s="38">
-        <f>J120+L120</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I120" s="37">
@@ -5944,97 +5962,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="31" t="s">
+    <row r="121" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="33">
+        <v>3</v>
+      </c>
+      <c r="B121" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="C121" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="D121" s="36">
+        <v>3</v>
+      </c>
+      <c r="E121" s="36">
+        <v>29.4862</v>
+      </c>
+      <c r="F121" s="36">
+        <f>+E121*D121</f>
+        <v>88.458600000000004</v>
+      </c>
+      <c r="G121" s="37">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="H121" s="38">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I121" s="37">
+        <f>J121/F121</f>
+        <v>0</v>
+      </c>
+      <c r="J121" s="38">
+        <v>0</v>
+      </c>
+      <c r="K121" s="37">
+        <f>L121/F121</f>
+        <v>0</v>
+      </c>
+      <c r="L121" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="B121" s="40" t="s">
+      <c r="B122" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="C121" s="41">
-        <v>0</v>
-      </c>
-      <c r="D121" s="42"/>
-      <c r="E121" s="42"/>
-      <c r="F121" s="42"/>
-      <c r="G121" s="43"/>
-      <c r="H121" s="44"/>
-      <c r="I121" s="43"/>
-      <c r="J121" s="44"/>
-      <c r="K121" s="43"/>
-      <c r="L121" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="33">
+      <c r="C122" s="41">
+        <v>0</v>
+      </c>
+      <c r="D122" s="42"/>
+      <c r="E122" s="42"/>
+      <c r="F122" s="42"/>
+      <c r="G122" s="43"/>
+      <c r="H122" s="44"/>
+      <c r="I122" s="43"/>
+      <c r="J122" s="44"/>
+      <c r="K122" s="43"/>
+      <c r="L122" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="33">
         <v>1</v>
       </c>
-      <c r="B122" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C122" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D122" s="36">
-        <v>0.33</v>
-      </c>
-      <c r="E122" s="36">
-        <v>803.44180000000006</v>
-      </c>
-      <c r="F122" s="36">
-        <f>+E122*D122</f>
-        <v>265.13579400000003</v>
-      </c>
-      <c r="G122" s="37">
-        <f t="shared" ref="G122:H124" si="21">I122+K122</f>
-        <v>0</v>
-      </c>
-      <c r="H122" s="38">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="I122" s="37">
-        <f>J122/F122</f>
-        <v>0</v>
-      </c>
-      <c r="J122" s="38">
-        <v>0</v>
-      </c>
-      <c r="K122" s="37">
-        <f>L122/F122</f>
-        <v>0</v>
-      </c>
-      <c r="L122" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="33">
-        <v>2</v>
-      </c>
       <c r="B123" s="34" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="C123" s="35" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D123" s="36">
-        <v>27.64</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="E123" s="36">
-        <v>19.7758</v>
+        <v>117.2572</v>
       </c>
       <c r="F123" s="36">
         <f>+E123*D123</f>
-        <v>546.60311200000001</v>
+        <v>991.99591200000009</v>
       </c>
       <c r="G123" s="37">
-        <f t="shared" si="21"/>
+        <f>I123+K123</f>
         <v>0</v>
       </c>
       <c r="H123" s="38">
-        <f t="shared" si="21"/>
+        <f>J123+L123</f>
         <v>0</v>
       </c>
       <c r="I123" s="37">
@@ -6053,161 +6071,161 @@
       </c>
     </row>
     <row r="124" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="33">
-        <v>3</v>
-      </c>
-      <c r="B124" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="C124" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="D124" s="36">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="E124" s="36">
-        <v>14.3188</v>
-      </c>
-      <c r="F124" s="36">
-        <f>+E124*D124</f>
-        <v>252.01088000000001</v>
-      </c>
-      <c r="G124" s="37">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="H124" s="38">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="I124" s="37">
-        <f>J124/F124</f>
-        <v>0</v>
-      </c>
-      <c r="J124" s="38">
-        <v>0</v>
-      </c>
-      <c r="K124" s="37">
-        <f>L124/F124</f>
-        <v>0</v>
-      </c>
-      <c r="L124" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="B125" s="40" t="s">
+      <c r="A124" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="C125" s="41">
-        <v>0</v>
-      </c>
-      <c r="D125" s="42"/>
-      <c r="E125" s="42"/>
-      <c r="F125" s="42"/>
-      <c r="G125" s="43"/>
-      <c r="H125" s="44"/>
-      <c r="I125" s="43"/>
-      <c r="J125" s="44"/>
-      <c r="K125" s="43"/>
-      <c r="L125" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="33">
+      <c r="B124" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C124" s="41">
+        <v>0</v>
+      </c>
+      <c r="D124" s="42"/>
+      <c r="E124" s="42"/>
+      <c r="F124" s="42"/>
+      <c r="G124" s="43"/>
+      <c r="H124" s="44"/>
+      <c r="I124" s="43"/>
+      <c r="J124" s="44"/>
+      <c r="K124" s="43"/>
+      <c r="L124" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="33">
         <v>1</v>
       </c>
-      <c r="B126" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="C126" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D126" s="36">
-        <v>16</v>
-      </c>
-      <c r="E126" s="36">
-        <v>32.403399999999998</v>
-      </c>
-      <c r="F126" s="36">
-        <f>+E126*D126</f>
-        <v>518.45439999999996</v>
-      </c>
-      <c r="G126" s="37">
-        <f>I126+K126</f>
-        <v>0</v>
-      </c>
-      <c r="H126" s="38">
-        <f>J126+L126</f>
-        <v>0</v>
-      </c>
-      <c r="I126" s="37">
-        <f>J126/F126</f>
-        <v>0</v>
-      </c>
-      <c r="J126" s="38">
-        <v>0</v>
-      </c>
-      <c r="K126" s="37">
-        <f>L126/F126</f>
-        <v>0</v>
-      </c>
-      <c r="L126" s="38">
+      <c r="B125" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="C125" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D125" s="36">
+        <v>2.91</v>
+      </c>
+      <c r="E125" s="36">
+        <v>255</v>
+      </c>
+      <c r="F125" s="36">
+        <f>+E125*D125</f>
+        <v>742.05000000000007</v>
+      </c>
+      <c r="G125" s="37">
+        <f>I125+K125</f>
+        <v>0</v>
+      </c>
+      <c r="H125" s="38">
+        <f>J125+L125</f>
+        <v>0</v>
+      </c>
+      <c r="I125" s="37">
+        <f>J125/F125</f>
+        <v>0</v>
+      </c>
+      <c r="J125" s="38">
+        <v>0</v>
+      </c>
+      <c r="K125" s="37">
+        <f>L125/F125</f>
+        <v>0</v>
+      </c>
+      <c r="L125" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="B126" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="C126" s="41">
+        <v>0</v>
+      </c>
+      <c r="D126" s="42"/>
+      <c r="E126" s="42"/>
+      <c r="F126" s="42"/>
+      <c r="G126" s="43"/>
+      <c r="H126" s="44"/>
+      <c r="I126" s="43"/>
+      <c r="J126" s="44"/>
+      <c r="K126" s="43"/>
+      <c r="L126" s="44">
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="B127" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="C127" s="41">
-        <v>0</v>
-      </c>
-      <c r="D127" s="42"/>
-      <c r="E127" s="42"/>
-      <c r="F127" s="42"/>
-      <c r="G127" s="43"/>
-      <c r="H127" s="44"/>
-      <c r="I127" s="43"/>
-      <c r="J127" s="44"/>
-      <c r="K127" s="43"/>
-      <c r="L127" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="33">
+        <v>1</v>
+      </c>
+      <c r="B127" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C127" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D127" s="36">
+        <v>0.33</v>
+      </c>
+      <c r="E127" s="36">
+        <v>803.44180000000006</v>
+      </c>
+      <c r="F127" s="36">
+        <f>+E127*D127</f>
+        <v>265.13579400000003</v>
+      </c>
+      <c r="G127" s="37">
+        <f t="shared" ref="G127:H129" si="22">I127+K127</f>
+        <v>0</v>
+      </c>
+      <c r="H127" s="38">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="I127" s="37">
+        <f>J127/F127</f>
+        <v>0</v>
+      </c>
+      <c r="J127" s="38">
+        <v>0</v>
+      </c>
+      <c r="K127" s="37">
+        <f>L127/F127</f>
+        <v>0</v>
+      </c>
+      <c r="L127" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A128" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B128" s="34" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="C128" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D128" s="36">
-        <v>63.4</v>
+        <v>27.64</v>
       </c>
       <c r="E128" s="36">
-        <v>10.320399999999999</v>
+        <v>19.7758</v>
       </c>
       <c r="F128" s="36">
         <f>+E128*D128</f>
-        <v>654.31335999999999</v>
+        <v>546.60311200000001</v>
       </c>
       <c r="G128" s="37">
-        <f>I128+K128</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H128" s="38">
-        <f>J128+L128</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I128" s="37">
@@ -6226,89 +6244,89 @@
       </c>
     </row>
     <row r="129" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="B129" s="40" t="s">
+      <c r="A129" s="33">
+        <v>3</v>
+      </c>
+      <c r="B129" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C129" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D129" s="36">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="E129" s="36">
+        <v>14.3188</v>
+      </c>
+      <c r="F129" s="36">
+        <f>+E129*D129</f>
+        <v>252.01088000000001</v>
+      </c>
+      <c r="G129" s="37">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="H129" s="38">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="I129" s="37">
+        <f>J129/F129</f>
+        <v>0</v>
+      </c>
+      <c r="J129" s="38">
+        <v>0</v>
+      </c>
+      <c r="K129" s="37">
+        <f>L129/F129</f>
+        <v>0</v>
+      </c>
+      <c r="L129" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="C129" s="41">
-        <v>0</v>
-      </c>
-      <c r="D129" s="42"/>
-      <c r="E129" s="42"/>
-      <c r="F129" s="42"/>
-      <c r="G129" s="43"/>
-      <c r="H129" s="44"/>
-      <c r="I129" s="43"/>
-      <c r="J129" s="44"/>
-      <c r="K129" s="43"/>
-      <c r="L129" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="33">
+      <c r="B130" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="C130" s="41">
+        <v>0</v>
+      </c>
+      <c r="D130" s="42"/>
+      <c r="E130" s="42"/>
+      <c r="F130" s="42"/>
+      <c r="G130" s="43"/>
+      <c r="H130" s="44"/>
+      <c r="I130" s="43"/>
+      <c r="J130" s="44"/>
+      <c r="K130" s="43"/>
+      <c r="L130" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="33">
         <v>1</v>
       </c>
-      <c r="B130" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="C130" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D130" s="36">
-        <v>18.5</v>
-      </c>
-      <c r="E130" s="36">
-        <v>117.15519999999999</v>
-      </c>
-      <c r="F130" s="36">
-        <f>+E130*D130</f>
-        <v>2167.3712</v>
-      </c>
-      <c r="G130" s="37">
-        <f>I130+K130</f>
-        <v>0</v>
-      </c>
-      <c r="H130" s="38">
-        <f>J130+L130</f>
-        <v>0</v>
-      </c>
-      <c r="I130" s="37">
-        <f>J130/F130</f>
-        <v>0</v>
-      </c>
-      <c r="J130" s="38">
-        <v>0</v>
-      </c>
-      <c r="K130" s="37">
-        <f>L130/F130</f>
-        <v>0</v>
-      </c>
-      <c r="L130" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="33">
-        <v>2</v>
-      </c>
       <c r="B131" s="34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C131" s="35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D131" s="36">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E131" s="36">
-        <v>117.15519999999999</v>
+        <v>32.403399999999998</v>
       </c>
       <c r="F131" s="36">
         <f>+E131*D131</f>
-        <v>1710.4659199999999</v>
+        <v>518.45439999999996</v>
       </c>
       <c r="G131" s="37">
         <f>I131+K131</f>
@@ -6335,10 +6353,10 @@
     </row>
     <row r="132" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A132" s="31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B132" s="40" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C132" s="41">
         <v>0</v>
@@ -6360,38 +6378,38 @@
         <v>1</v>
       </c>
       <c r="B133" s="34" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="C133" s="35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D133" s="36">
-        <v>3.35</v>
+        <v>63.4</v>
       </c>
       <c r="E133" s="36">
-        <v>117.2572</v>
+        <v>10.320399999999999</v>
       </c>
       <c r="F133" s="36">
-        <f t="shared" ref="F133:F139" si="22">+E133*D133</f>
-        <v>392.81162</v>
+        <f>+E133*D133</f>
+        <v>654.31335999999999</v>
       </c>
       <c r="G133" s="37">
-        <f t="shared" ref="G133:H139" si="23">I133+K133</f>
+        <f>I133+K133</f>
         <v>0</v>
       </c>
       <c r="H133" s="38">
-        <f t="shared" si="23"/>
+        <f>J133+L133</f>
         <v>0</v>
       </c>
       <c r="I133" s="37">
-        <f t="shared" ref="I133:I139" si="24">J133/F133</f>
+        <f>J133/F133</f>
         <v>0</v>
       </c>
       <c r="J133" s="38">
         <v>0</v>
       </c>
       <c r="K133" s="37">
-        <f t="shared" ref="K133:K139" si="25">L133/F133</f>
+        <f>L133/F133</f>
         <v>0</v>
       </c>
       <c r="L133" s="38">
@@ -6399,688 +6417,667 @@
       </c>
     </row>
     <row r="134" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="33">
-        <v>2</v>
-      </c>
-      <c r="B134" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="C134" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D134" s="36">
-        <v>12.5</v>
-      </c>
-      <c r="E134" s="36">
-        <v>40.247199999999999</v>
-      </c>
-      <c r="F134" s="36">
-        <f t="shared" si="22"/>
-        <v>503.09</v>
-      </c>
-      <c r="G134" s="37">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="H134" s="38">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="I134" s="37">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="J134" s="38">
-        <v>0</v>
-      </c>
-      <c r="K134" s="37">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="L134" s="38">
+      <c r="A134" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="B134" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="C134" s="41">
+        <v>0</v>
+      </c>
+      <c r="D134" s="42"/>
+      <c r="E134" s="42"/>
+      <c r="F134" s="42"/>
+      <c r="G134" s="43"/>
+      <c r="H134" s="44"/>
+      <c r="I134" s="43"/>
+      <c r="J134" s="44"/>
+      <c r="K134" s="43"/>
+      <c r="L134" s="44">
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A135" s="33">
+        <v>1</v>
+      </c>
+      <c r="B135" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="C135" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D135" s="36">
+        <v>18.5</v>
+      </c>
+      <c r="E135" s="36">
+        <v>117.15519999999999</v>
+      </c>
+      <c r="F135" s="36">
+        <f>+E135*D135</f>
+        <v>2167.3712</v>
+      </c>
+      <c r="G135" s="37">
+        <f>I135+K135</f>
+        <v>0</v>
+      </c>
+      <c r="H135" s="38">
+        <f>J135+L135</f>
+        <v>0</v>
+      </c>
+      <c r="I135" s="37">
+        <f>J135/F135</f>
+        <v>0</v>
+      </c>
+      <c r="J135" s="38">
+        <v>0</v>
+      </c>
+      <c r="K135" s="37">
+        <f>L135/F135</f>
+        <v>0</v>
+      </c>
+      <c r="L135" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="33">
+        <v>2</v>
+      </c>
+      <c r="B136" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="C136" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D136" s="36">
+        <v>14.6</v>
+      </c>
+      <c r="E136" s="36">
+        <v>117.15519999999999</v>
+      </c>
+      <c r="F136" s="36">
+        <f>+E136*D136</f>
+        <v>1710.4659199999999</v>
+      </c>
+      <c r="G136" s="37">
+        <f>I136+K136</f>
+        <v>0</v>
+      </c>
+      <c r="H136" s="38">
+        <f>J136+L136</f>
+        <v>0</v>
+      </c>
+      <c r="I136" s="37">
+        <f>J136/F136</f>
+        <v>0</v>
+      </c>
+      <c r="J136" s="38">
+        <v>0</v>
+      </c>
+      <c r="K136" s="37">
+        <f>L136/F136</f>
+        <v>0</v>
+      </c>
+      <c r="L136" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B137" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="C137" s="41">
+        <v>0</v>
+      </c>
+      <c r="D137" s="42"/>
+      <c r="E137" s="42"/>
+      <c r="F137" s="42"/>
+      <c r="G137" s="43"/>
+      <c r="H137" s="44"/>
+      <c r="I137" s="43"/>
+      <c r="J137" s="44"/>
+      <c r="K137" s="43"/>
+      <c r="L137" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="33">
+        <v>1</v>
+      </c>
+      <c r="B138" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="C138" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D138" s="36">
+        <v>3.35</v>
+      </c>
+      <c r="E138" s="36">
+        <v>117.2572</v>
+      </c>
+      <c r="F138" s="36">
+        <f t="shared" ref="F138:F144" si="23">+E138*D138</f>
+        <v>392.81162</v>
+      </c>
+      <c r="G138" s="37">
+        <f t="shared" ref="G138:H144" si="24">I138+K138</f>
+        <v>0</v>
+      </c>
+      <c r="H138" s="38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="I138" s="37">
+        <f t="shared" ref="I138:I144" si="25">J138/F138</f>
+        <v>0</v>
+      </c>
+      <c r="J138" s="38">
+        <v>0</v>
+      </c>
+      <c r="K138" s="37">
+        <f t="shared" ref="K138:K144" si="26">L138/F138</f>
+        <v>0</v>
+      </c>
+      <c r="L138" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="33">
+        <v>2</v>
+      </c>
+      <c r="B139" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="C139" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D139" s="36">
+        <v>12.5</v>
+      </c>
+      <c r="E139" s="36">
+        <v>40.247199999999999</v>
+      </c>
+      <c r="F139" s="36">
+        <f t="shared" si="23"/>
+        <v>503.09</v>
+      </c>
+      <c r="G139" s="37">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="H139" s="38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="I139" s="37">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="J139" s="38">
+        <v>0</v>
+      </c>
+      <c r="K139" s="37">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="L139" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="33">
         <v>3</v>
       </c>
-      <c r="B135" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="C135" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D135" s="36">
+      <c r="B140" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="C140" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D140" s="36">
         <v>5.14</v>
       </c>
-      <c r="E135" s="36">
+      <c r="E140" s="36">
         <v>5.4244000000000003</v>
       </c>
-      <c r="F135" s="36">
-        <f t="shared" si="22"/>
+      <c r="F140" s="36">
+        <f t="shared" si="23"/>
         <v>27.881416000000002</v>
       </c>
-      <c r="G135" s="37">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="H135" s="38">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="I135" s="37">
+      <c r="G140" s="37">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J135" s="38">
-        <v>0</v>
-      </c>
-      <c r="K135" s="37">
+      <c r="H140" s="38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="I140" s="37">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="L135" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="33">
+      <c r="J140" s="38">
+        <v>0</v>
+      </c>
+      <c r="K140" s="37">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="L140" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="33">
         <v>4</v>
-      </c>
-      <c r="B136" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="C136" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D136" s="36">
-        <v>5.14</v>
-      </c>
-      <c r="E136" s="36">
-        <v>32.403399999999998</v>
-      </c>
-      <c r="F136" s="36">
-        <f t="shared" si="22"/>
-        <v>166.55347599999999</v>
-      </c>
-      <c r="G136" s="37">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="H136" s="38">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="I136" s="37">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="J136" s="38">
-        <v>0</v>
-      </c>
-      <c r="K136" s="37">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="L136" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="33">
-        <v>5</v>
-      </c>
-      <c r="B137" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="C137" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D137" s="36">
-        <v>5.46</v>
-      </c>
-      <c r="E137" s="36">
-        <v>27.079000000000001</v>
-      </c>
-      <c r="F137" s="36">
-        <f t="shared" si="22"/>
-        <v>147.85133999999999</v>
-      </c>
-      <c r="G137" s="37">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="H137" s="38">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="I137" s="37">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="J137" s="38">
-        <v>0</v>
-      </c>
-      <c r="K137" s="37">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="L137" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="33">
-        <v>6</v>
-      </c>
-      <c r="B138" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="C138" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D138" s="36">
-        <v>34</v>
-      </c>
-      <c r="E138" s="36">
-        <v>10.8202</v>
-      </c>
-      <c r="F138" s="36">
-        <f t="shared" si="22"/>
-        <v>367.88679999999999</v>
-      </c>
-      <c r="G138" s="37">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="H138" s="38">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="I138" s="37">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="J138" s="38">
-        <v>0</v>
-      </c>
-      <c r="K138" s="37">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="L138" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="33">
-        <v>7</v>
-      </c>
-      <c r="B139" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="C139" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D139" s="36">
-        <v>34</v>
-      </c>
-      <c r="E139" s="36">
-        <v>40.186</v>
-      </c>
-      <c r="F139" s="36">
-        <f t="shared" si="22"/>
-        <v>1366.3240000000001</v>
-      </c>
-      <c r="G139" s="37">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="H139" s="38">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="I139" s="37">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="J139" s="38">
-        <v>0</v>
-      </c>
-      <c r="K139" s="37">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="L139" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="B140" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="C140" s="41">
-        <v>0</v>
-      </c>
-      <c r="D140" s="42"/>
-      <c r="E140" s="42"/>
-      <c r="F140" s="42"/>
-      <c r="G140" s="43"/>
-      <c r="H140" s="44"/>
-      <c r="I140" s="43"/>
-      <c r="J140" s="44"/>
-      <c r="K140" s="43"/>
-      <c r="L140" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="33">
-        <v>1</v>
       </c>
       <c r="B141" s="34" t="s">
         <v>170</v>
       </c>
       <c r="C141" s="35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D141" s="36">
-        <v>8683</v>
+        <v>5.14</v>
       </c>
       <c r="E141" s="36">
-        <v>0.9</v>
+        <v>32.403399999999998</v>
       </c>
       <c r="F141" s="36">
-        <f t="shared" ref="F141:F148" si="26">+E141*D141</f>
-        <v>7814.7</v>
+        <f t="shared" si="23"/>
+        <v>166.55347599999999</v>
       </c>
       <c r="G141" s="37">
-        <f t="shared" ref="G141:H148" si="27">I141+K141</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H141" s="38">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I141" s="37">
-        <f t="shared" ref="I141:I148" si="28">J141/F141</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J141" s="38">
         <v>0</v>
       </c>
       <c r="K141" s="37">
-        <f t="shared" ref="K141:K148" si="29">L141/F141</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="L141" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A142" s="33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B142" s="34" t="s">
         <v>171</v>
       </c>
       <c r="C142" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D142" s="36">
+        <v>5.46</v>
+      </c>
+      <c r="E142" s="36">
+        <v>27.079000000000001</v>
+      </c>
+      <c r="F142" s="36">
+        <f t="shared" si="23"/>
+        <v>147.85133999999999</v>
+      </c>
+      <c r="G142" s="37">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="H142" s="38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="I142" s="37">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="J142" s="38">
+        <v>0</v>
+      </c>
+      <c r="K142" s="37">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="L142" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="33">
+        <v>6</v>
+      </c>
+      <c r="B143" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="D142" s="36">
-        <v>15195.25</v>
-      </c>
-      <c r="E142" s="36">
-        <v>1.63</v>
-      </c>
-      <c r="F142" s="36">
+      <c r="C143" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D143" s="36">
+        <v>34</v>
+      </c>
+      <c r="E143" s="36">
+        <v>10.8202</v>
+      </c>
+      <c r="F143" s="36">
+        <f t="shared" si="23"/>
+        <v>367.88679999999999</v>
+      </c>
+      <c r="G143" s="37">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="H143" s="38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="I143" s="37">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="J143" s="38">
+        <v>0</v>
+      </c>
+      <c r="K143" s="37">
         <f t="shared" si="26"/>
-        <v>24768.2575</v>
-      </c>
-      <c r="G142" s="37">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="H142" s="38">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I142" s="37">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="J142" s="38">
-        <v>0</v>
-      </c>
-      <c r="K142" s="37">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="L142" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="33">
-        <v>3</v>
-      </c>
-      <c r="B143" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="L143" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="33">
+        <v>7</v>
+      </c>
+      <c r="B144" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="C143" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D143" s="36">
-        <v>12996</v>
-      </c>
-      <c r="E143" s="36">
-        <v>0.9</v>
-      </c>
-      <c r="F143" s="36">
+      <c r="C144" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D144" s="36">
+        <v>34</v>
+      </c>
+      <c r="E144" s="36">
+        <v>40.186</v>
+      </c>
+      <c r="F144" s="36">
+        <f t="shared" si="23"/>
+        <v>1366.3240000000001</v>
+      </c>
+      <c r="G144" s="37">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="H144" s="38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="I144" s="37">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="J144" s="38">
+        <v>0</v>
+      </c>
+      <c r="K144" s="37">
         <f t="shared" si="26"/>
-        <v>11696.4</v>
-      </c>
-      <c r="G143" s="37">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="H143" s="38">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I143" s="37">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="J143" s="38">
-        <v>0</v>
-      </c>
-      <c r="K143" s="37">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="L143" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="33">
-        <v>4</v>
-      </c>
-      <c r="B144" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="L144" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="C144" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D144" s="36">
-        <v>12996</v>
-      </c>
-      <c r="E144" s="36">
-        <v>0.9</v>
-      </c>
-      <c r="F144" s="36">
-        <f t="shared" si="26"/>
-        <v>11696.4</v>
-      </c>
-      <c r="G144" s="37">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="H144" s="38">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I144" s="37">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="J144" s="38">
-        <v>0</v>
-      </c>
-      <c r="K144" s="37">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="L144" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="33">
-        <v>5</v>
-      </c>
-      <c r="B145" s="34" t="s">
+      <c r="B145" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="C145" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D145" s="36">
-        <v>12996</v>
-      </c>
-      <c r="E145" s="36">
-        <v>0.9</v>
-      </c>
-      <c r="F145" s="36">
-        <f t="shared" si="26"/>
-        <v>11696.4</v>
-      </c>
-      <c r="G145" s="37">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="H145" s="38">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I145" s="37">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="J145" s="38">
-        <v>0</v>
-      </c>
-      <c r="K145" s="37">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="L145" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C145" s="41">
+        <v>0</v>
+      </c>
+      <c r="D145" s="42"/>
+      <c r="E145" s="42"/>
+      <c r="F145" s="42"/>
+      <c r="G145" s="43"/>
+      <c r="H145" s="44"/>
+      <c r="I145" s="43"/>
+      <c r="J145" s="44"/>
+      <c r="K145" s="43"/>
+      <c r="L145" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A146" s="33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B146" s="34" t="s">
         <v>176</v>
       </c>
       <c r="C146" s="35" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D146" s="36">
-        <v>12996</v>
+        <v>8683</v>
       </c>
       <c r="E146" s="36">
         <v>0.9</v>
       </c>
       <c r="F146" s="36">
-        <f t="shared" si="26"/>
-        <v>11696.4</v>
+        <f t="shared" ref="F146:F153" si="27">+E146*D146</f>
+        <v>7814.7</v>
       </c>
       <c r="G146" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="G146:H153" si="28">I146+K146</f>
         <v>0</v>
       </c>
       <c r="H146" s="38">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="I146" s="37">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="I146:I153" si="29">J146/F146</f>
         <v>0</v>
       </c>
       <c r="J146" s="38">
         <v>0</v>
       </c>
       <c r="K146" s="37">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="K146:K153" si="30">L146/F146</f>
         <v>0</v>
       </c>
       <c r="L146" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A147" s="33">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B147" s="34" t="s">
         <v>177</v>
       </c>
       <c r="C147" s="35" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="D147" s="36">
-        <v>522</v>
+        <v>15195.25</v>
       </c>
       <c r="E147" s="36">
+        <v>1.63</v>
+      </c>
+      <c r="F147" s="36">
+        <f t="shared" si="27"/>
+        <v>24768.2575</v>
+      </c>
+      <c r="G147" s="37">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H147" s="38">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="I147" s="37">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J147" s="38">
+        <v>0</v>
+      </c>
+      <c r="K147" s="37">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="L147" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="33">
+        <v>3</v>
+      </c>
+      <c r="B148" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="C148" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D148" s="36">
+        <v>12996</v>
+      </c>
+      <c r="E148" s="36">
         <v>0.9</v>
       </c>
-      <c r="F147" s="36">
-        <f t="shared" si="26"/>
-        <v>469.8</v>
-      </c>
-      <c r="G147" s="37">
+      <c r="F148" s="36">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="H147" s="38">
+        <v>11696.4</v>
+      </c>
+      <c r="G148" s="37">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H148" s="38">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="I148" s="37">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J148" s="38">
+        <v>0</v>
+      </c>
+      <c r="K148" s="37">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="L148" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="33">
+        <v>4</v>
+      </c>
+      <c r="B149" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C149" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D149" s="36">
+        <v>12996</v>
+      </c>
+      <c r="E149" s="36">
+        <v>0.9</v>
+      </c>
+      <c r="F149" s="36">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I147" s="37">
+        <v>11696.4</v>
+      </c>
+      <c r="G149" s="37">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="J147" s="38">
-        <v>0</v>
-      </c>
-      <c r="K147" s="37">
+      <c r="H149" s="38">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="I149" s="37">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L147" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="33">
-        <v>8</v>
-      </c>
-      <c r="B148" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="C148" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="D148" s="36">
-        <v>626.4</v>
-      </c>
-      <c r="E148" s="36">
-        <v>1.63</v>
-      </c>
-      <c r="F148" s="36">
-        <f t="shared" si="26"/>
-        <v>1021.0319999999999</v>
-      </c>
-      <c r="G148" s="37">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="H148" s="38">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I148" s="37">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="J148" s="38">
-        <v>0</v>
-      </c>
-      <c r="K148" s="37">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="L148" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="B149" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="C149" s="41">
-        <v>0</v>
-      </c>
-      <c r="D149" s="42"/>
-      <c r="E149" s="42"/>
-      <c r="F149" s="42"/>
-      <c r="G149" s="43"/>
-      <c r="H149" s="44"/>
-      <c r="I149" s="43"/>
-      <c r="J149" s="44"/>
-      <c r="K149" s="43"/>
-      <c r="L149" s="44">
+      <c r="J149" s="38">
+        <v>0</v>
+      </c>
+      <c r="K149" s="37">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="L149" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A150" s="33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B150" s="34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C150" s="35" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D150" s="36">
-        <v>599.70000000000005</v>
+        <v>12996</v>
       </c>
       <c r="E150" s="36">
-        <v>4.1891800000000003</v>
+        <v>0.9</v>
       </c>
       <c r="F150" s="36">
-        <f t="shared" ref="F150:F155" si="30">+E150*D150</f>
-        <v>2512.2512460000003</v>
+        <f t="shared" si="27"/>
+        <v>11696.4</v>
       </c>
       <c r="G150" s="37">
-        <f t="shared" ref="G150:H155" si="31">I150+K150</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H150" s="38">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="I150" s="37">
-        <f t="shared" ref="I150:I155" si="32">J150/F150</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="J150" s="38">
         <v>0</v>
       </c>
       <c r="K150" s="37">
-        <f t="shared" ref="K150:K155" si="33">L150/F150</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="L150" s="38">
@@ -7089,84 +7086,84 @@
     </row>
     <row r="151" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A151" s="33">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B151" s="34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C151" s="35" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D151" s="36">
-        <v>383.7</v>
+        <v>12996</v>
       </c>
       <c r="E151" s="36">
-        <v>0.81122000000000005</v>
+        <v>0.9</v>
       </c>
       <c r="F151" s="36">
+        <f t="shared" si="27"/>
+        <v>11696.4</v>
+      </c>
+      <c r="G151" s="37">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H151" s="38">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="I151" s="37">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J151" s="38">
+        <v>0</v>
+      </c>
+      <c r="K151" s="37">
         <f t="shared" si="30"/>
-        <v>311.26511399999998</v>
-      </c>
-      <c r="G151" s="37">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H151" s="38">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="I151" s="37">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J151" s="38">
-        <v>0</v>
-      </c>
-      <c r="K151" s="37">
-        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L151" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A152" s="33">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B152" s="34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C152" s="35" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D152" s="36">
-        <v>383.7</v>
+        <v>522</v>
       </c>
       <c r="E152" s="36">
-        <v>7.0788399999999996</v>
+        <v>0.9</v>
       </c>
       <c r="F152" s="36">
+        <f t="shared" si="27"/>
+        <v>469.8</v>
+      </c>
+      <c r="G152" s="37">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H152" s="38">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="I152" s="37">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J152" s="38">
+        <v>0</v>
+      </c>
+      <c r="K152" s="37">
         <f t="shared" si="30"/>
-        <v>2716.1509079999996</v>
-      </c>
-      <c r="G152" s="37">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H152" s="38">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="I152" s="37">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J152" s="38">
-        <v>0</v>
-      </c>
-      <c r="K152" s="37">
-        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L152" s="38">
@@ -7175,192 +7172,192 @@
     </row>
     <row r="153" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A153" s="33">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B153" s="34" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C153" s="35" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="D153" s="36">
-        <v>383.7</v>
+        <v>626.4</v>
       </c>
       <c r="E153" s="36">
-        <v>4.6726599999999996</v>
+        <v>1.63</v>
       </c>
       <c r="F153" s="36">
+        <f t="shared" si="27"/>
+        <v>1021.0319999999999</v>
+      </c>
+      <c r="G153" s="37">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H153" s="38">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="I153" s="37">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J153" s="38">
+        <v>0</v>
+      </c>
+      <c r="K153" s="37">
         <f t="shared" si="30"/>
-        <v>1792.8996419999999</v>
-      </c>
-      <c r="G153" s="37">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H153" s="38">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="I153" s="37">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J153" s="38">
-        <v>0</v>
-      </c>
-      <c r="K153" s="37">
-        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L153" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="33">
-        <v>5</v>
-      </c>
-      <c r="B154" s="34" t="s">
+    <row r="154" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="C154" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D154" s="36">
-        <v>383.7</v>
-      </c>
-      <c r="E154" s="36">
-        <v>7.1288199999999993</v>
-      </c>
-      <c r="F154" s="36">
-        <f t="shared" si="30"/>
-        <v>2735.3282339999996</v>
-      </c>
-      <c r="G154" s="37">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H154" s="38">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="I154" s="37">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J154" s="38">
-        <v>0</v>
-      </c>
-      <c r="K154" s="37">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="L154" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B154" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="C154" s="41">
+        <v>0</v>
+      </c>
+      <c r="D154" s="42"/>
+      <c r="E154" s="42"/>
+      <c r="F154" s="42"/>
+      <c r="G154" s="43"/>
+      <c r="H154" s="44"/>
+      <c r="I154" s="43"/>
+      <c r="J154" s="44"/>
+      <c r="K154" s="43"/>
+      <c r="L154" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A155" s="33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B155" s="34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C155" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D155" s="36">
         <v>383.7</v>
       </c>
       <c r="E155" s="36">
-        <v>1.7259199999999999</v>
+        <v>4.1891800000000003</v>
       </c>
       <c r="F155" s="36">
-        <f t="shared" si="30"/>
-        <v>662.23550399999999</v>
+        <f t="shared" ref="F155:F160" si="31">+E155*D155</f>
+        <v>1607.3883660000001</v>
       </c>
       <c r="G155" s="37">
+        <f t="shared" ref="G155:H160" si="32">I155+K155</f>
+        <v>0</v>
+      </c>
+      <c r="H155" s="38">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="I155" s="37">
+        <f t="shared" ref="I155:I160" si="33">J155/F155</f>
+        <v>0</v>
+      </c>
+      <c r="J155" s="38">
+        <v>0</v>
+      </c>
+      <c r="K155" s="37">
+        <f t="shared" ref="K155:K160" si="34">L155/F155</f>
+        <v>0</v>
+      </c>
+      <c r="L155" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="33">
+        <v>2</v>
+      </c>
+      <c r="B156" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="C156" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D156" s="36">
+        <v>383.7</v>
+      </c>
+      <c r="E156" s="36">
+        <v>0.81122000000000005</v>
+      </c>
+      <c r="F156" s="36">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H155" s="38">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="I155" s="37">
+        <v>311.26511399999998</v>
+      </c>
+      <c r="G156" s="37">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="J155" s="38">
-        <v>0</v>
-      </c>
-      <c r="K155" s="37">
+      <c r="H156" s="38">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="I156" s="37">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="L155" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="B156" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="C156" s="41">
-        <v>0</v>
-      </c>
-      <c r="D156" s="42"/>
-      <c r="E156" s="42"/>
-      <c r="F156" s="42"/>
-      <c r="G156" s="43"/>
-      <c r="H156" s="44"/>
-      <c r="I156" s="43"/>
-      <c r="J156" s="44"/>
-      <c r="K156" s="43"/>
-      <c r="L156" s="44">
+      <c r="J156" s="38">
+        <v>0</v>
+      </c>
+      <c r="K156" s="37">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="L156" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A157" s="33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B157" s="34" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C157" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D157" s="36">
-        <v>599.70000000000005</v>
+        <v>383.7</v>
       </c>
       <c r="E157" s="36">
-        <v>4.1891800000000003</v>
+        <v>7.0788399999999996</v>
       </c>
       <c r="F157" s="36">
-        <f t="shared" ref="F157:F162" si="34">+E157*D157</f>
-        <v>2512.2512460000003</v>
+        <f t="shared" si="31"/>
+        <v>2716.1509079999996</v>
       </c>
       <c r="G157" s="37">
-        <f t="shared" ref="G157:H162" si="35">I157+K157</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H157" s="38">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I157" s="37">
-        <f t="shared" ref="I157:I162" si="36">J157/F157</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J157" s="38">
         <v>0</v>
       </c>
       <c r="K157" s="37">
-        <f t="shared" ref="K157:K162" si="37">L157/F157</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L157" s="38">
@@ -7369,84 +7366,84 @@
     </row>
     <row r="158" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A158" s="33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B158" s="34" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C158" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D158" s="36">
-        <v>216</v>
+        <v>383.7</v>
       </c>
       <c r="E158" s="36">
-        <v>0.9</v>
+        <v>4.6726599999999996</v>
       </c>
       <c r="F158" s="36">
+        <f t="shared" si="31"/>
+        <v>1792.8996419999999</v>
+      </c>
+      <c r="G158" s="37">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H158" s="38">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="I158" s="37">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="J158" s="38">
+        <v>0</v>
+      </c>
+      <c r="K158" s="37">
         <f t="shared" si="34"/>
-        <v>194.4</v>
-      </c>
-      <c r="G158" s="37">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="H158" s="38">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="I158" s="37">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J158" s="38">
-        <v>0</v>
-      </c>
-      <c r="K158" s="37">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="L158" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A159" s="33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B159" s="34" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C159" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D159" s="36">
-        <v>216</v>
+        <v>383.7</v>
       </c>
       <c r="E159" s="36">
-        <v>7.0768000000000004</v>
+        <v>7.1288199999999993</v>
       </c>
       <c r="F159" s="36">
+        <f t="shared" si="31"/>
+        <v>2735.3282339999996</v>
+      </c>
+      <c r="G159" s="37">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H159" s="38">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="I159" s="37">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="J159" s="38">
+        <v>0</v>
+      </c>
+      <c r="K159" s="37">
         <f t="shared" si="34"/>
-        <v>1528.5888</v>
-      </c>
-      <c r="G159" s="37">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="H159" s="38">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="I159" s="37">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J159" s="38">
-        <v>0</v>
-      </c>
-      <c r="K159" s="37">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="L159" s="38">
@@ -7455,192 +7452,192 @@
     </row>
     <row r="160" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A160" s="33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B160" s="34" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C160" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D160" s="36">
-        <v>216</v>
+        <v>383.7</v>
       </c>
       <c r="E160" s="36">
-        <v>4.6185999999999998</v>
+        <v>1.7259199999999999</v>
       </c>
       <c r="F160" s="36">
+        <f t="shared" si="31"/>
+        <v>662.23550399999999</v>
+      </c>
+      <c r="G160" s="37">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H160" s="38">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="I160" s="37">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="J160" s="38">
+        <v>0</v>
+      </c>
+      <c r="K160" s="37">
         <f t="shared" si="34"/>
-        <v>997.61759999999992</v>
-      </c>
-      <c r="G160" s="37">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="H160" s="38">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="I160" s="37">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J160" s="38">
-        <v>0</v>
-      </c>
-      <c r="K160" s="37">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="L160" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="33">
-        <v>5</v>
-      </c>
-      <c r="B161" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="C161" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D161" s="36">
-        <v>216</v>
-      </c>
-      <c r="E161" s="36">
-        <v>7.1176000000000004</v>
-      </c>
-      <c r="F161" s="36">
-        <f t="shared" si="34"/>
-        <v>1537.4016000000001</v>
-      </c>
-      <c r="G161" s="37">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="H161" s="38">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="I161" s="37">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J161" s="38">
-        <v>0</v>
-      </c>
-      <c r="K161" s="37">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="L161" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="B161" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="C161" s="41">
+        <v>0</v>
+      </c>
+      <c r="D161" s="42"/>
+      <c r="E161" s="42"/>
+      <c r="F161" s="42"/>
+      <c r="G161" s="43"/>
+      <c r="H161" s="44"/>
+      <c r="I161" s="43"/>
+      <c r="J161" s="44"/>
+      <c r="K161" s="43"/>
+      <c r="L161" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A162" s="33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B162" s="34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C162" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D162" s="36">
         <v>216</v>
       </c>
       <c r="E162" s="36">
-        <v>1.7259199999999999</v>
+        <v>4.1891800000000003</v>
       </c>
       <c r="F162" s="36">
-        <f t="shared" si="34"/>
-        <v>372.79872</v>
+        <f t="shared" ref="F162:F167" si="35">+E162*D162</f>
+        <v>904.86288000000013</v>
       </c>
       <c r="G162" s="37">
+        <f t="shared" ref="G162:H167" si="36">I162+K162</f>
+        <v>0</v>
+      </c>
+      <c r="H162" s="38">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="I162" s="37">
+        <f t="shared" ref="I162:I167" si="37">J162/F162</f>
+        <v>0</v>
+      </c>
+      <c r="J162" s="38">
+        <v>0</v>
+      </c>
+      <c r="K162" s="37">
+        <f t="shared" ref="K162:K167" si="38">L162/F162</f>
+        <v>0</v>
+      </c>
+      <c r="L162" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="33">
+        <v>2</v>
+      </c>
+      <c r="B163" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="C163" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D163" s="36">
+        <v>216</v>
+      </c>
+      <c r="E163" s="36">
+        <v>0.9</v>
+      </c>
+      <c r="F163" s="36">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="H162" s="38">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="I162" s="37">
+        <v>194.4</v>
+      </c>
+      <c r="G163" s="37">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="J162" s="38">
-        <v>0</v>
-      </c>
-      <c r="K162" s="37">
+      <c r="H163" s="38">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="I163" s="37">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="L162" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="B163" s="40" t="s">
-        <v>189</v>
-      </c>
-      <c r="C163" s="41">
-        <v>0</v>
-      </c>
-      <c r="D163" s="42"/>
-      <c r="E163" s="42"/>
-      <c r="F163" s="42"/>
-      <c r="G163" s="43"/>
-      <c r="H163" s="44"/>
-      <c r="I163" s="43"/>
-      <c r="J163" s="44"/>
-      <c r="K163" s="43"/>
-      <c r="L163" s="44">
+      <c r="J163" s="38">
+        <v>0</v>
+      </c>
+      <c r="K163" s="37">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="L163" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A164" s="33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B164" s="34" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C164" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D164" s="36">
-        <v>1021</v>
+        <v>216</v>
       </c>
       <c r="E164" s="36">
-        <v>4.1891800000000003</v>
+        <v>7.0768000000000004</v>
       </c>
       <c r="F164" s="36">
-        <f t="shared" ref="F164:F169" si="38">+E164*D164</f>
-        <v>4277.1527800000003</v>
+        <f t="shared" si="35"/>
+        <v>1528.5888</v>
       </c>
       <c r="G164" s="37">
-        <f t="shared" ref="G164:H169" si="39">I164+K164</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H164" s="38">
-        <f t="shared" si="39"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="I164" s="37">
-        <f t="shared" ref="I164:I169" si="40">J164/F164</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="J164" s="38">
         <v>0</v>
       </c>
       <c r="K164" s="37">
-        <f t="shared" ref="K164:K169" si="41">L164/F164</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="L164" s="38">
@@ -7649,84 +7646,84 @@
     </row>
     <row r="165" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A165" s="33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B165" s="34" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C165" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D165" s="36">
-        <v>1021</v>
+        <v>216</v>
       </c>
       <c r="E165" s="36">
-        <v>0.9</v>
+        <v>4.6185999999999998</v>
       </c>
       <c r="F165" s="36">
+        <f t="shared" si="35"/>
+        <v>997.61759999999992</v>
+      </c>
+      <c r="G165" s="37">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="H165" s="38">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="I165" s="37">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="J165" s="38">
+        <v>0</v>
+      </c>
+      <c r="K165" s="37">
         <f t="shared" si="38"/>
-        <v>918.9</v>
-      </c>
-      <c r="G165" s="37">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="H165" s="38">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="I165" s="37">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="J165" s="38">
-        <v>0</v>
-      </c>
-      <c r="K165" s="37">
-        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L165" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A166" s="33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B166" s="34" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C166" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D166" s="36">
-        <v>1021</v>
+        <v>216</v>
       </c>
       <c r="E166" s="36">
-        <v>7.0768000000000004</v>
+        <v>7.1176000000000004</v>
       </c>
       <c r="F166" s="36">
+        <f t="shared" si="35"/>
+        <v>1537.4016000000001</v>
+      </c>
+      <c r="G166" s="37">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="H166" s="38">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="I166" s="37">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="J166" s="38">
+        <v>0</v>
+      </c>
+      <c r="K166" s="37">
         <f t="shared" si="38"/>
-        <v>7225.4128000000001</v>
-      </c>
-      <c r="G166" s="37">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="H166" s="38">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="I166" s="37">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="J166" s="38">
-        <v>0</v>
-      </c>
-      <c r="K166" s="37">
-        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L166" s="38">
@@ -7735,192 +7732,192 @@
     </row>
     <row r="167" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A167" s="33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B167" s="34" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C167" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D167" s="36">
-        <v>1021</v>
+        <v>216</v>
       </c>
       <c r="E167" s="36">
-        <v>4.7420599999999986</v>
+        <v>1.7259199999999999</v>
       </c>
       <c r="F167" s="36">
+        <f t="shared" si="35"/>
+        <v>372.79872</v>
+      </c>
+      <c r="G167" s="37">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="H167" s="38">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="I167" s="37">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="J167" s="38">
+        <v>0</v>
+      </c>
+      <c r="K167" s="37">
         <f t="shared" si="38"/>
-        <v>4841.6432599999989</v>
-      </c>
-      <c r="G167" s="37">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="H167" s="38">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="I167" s="37">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="J167" s="38">
-        <v>0</v>
-      </c>
-      <c r="K167" s="37">
-        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L167" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="33">
-        <v>5</v>
-      </c>
-      <c r="B168" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="C168" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D168" s="36">
-        <v>1021</v>
-      </c>
-      <c r="E168" s="36">
-        <v>7.1267799999999992</v>
-      </c>
-      <c r="F168" s="36">
-        <f t="shared" si="38"/>
-        <v>7276.4423799999995</v>
-      </c>
-      <c r="G168" s="37">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="H168" s="38">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="I168" s="37">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="J168" s="38">
-        <v>0</v>
-      </c>
-      <c r="K168" s="37">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="L168" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="B168" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="C168" s="41">
+        <v>0</v>
+      </c>
+      <c r="D168" s="42"/>
+      <c r="E168" s="42"/>
+      <c r="F168" s="42"/>
+      <c r="G168" s="43"/>
+      <c r="H168" s="44"/>
+      <c r="I168" s="43"/>
+      <c r="J168" s="44"/>
+      <c r="K168" s="43"/>
+      <c r="L168" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A169" s="33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B169" s="34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C169" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D169" s="36">
         <v>1021</v>
       </c>
       <c r="E169" s="36">
-        <v>1.7259199999999999</v>
+        <v>4.1891800000000003</v>
       </c>
       <c r="F169" s="36">
-        <f t="shared" si="38"/>
-        <v>1762.1643199999999</v>
+        <f t="shared" ref="F169:F174" si="39">+E169*D169</f>
+        <v>4277.1527800000003</v>
       </c>
       <c r="G169" s="37">
+        <f t="shared" ref="G169:H174" si="40">I169+K169</f>
+        <v>0</v>
+      </c>
+      <c r="H169" s="38">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="I169" s="37">
+        <f t="shared" ref="I169:I174" si="41">J169/F169</f>
+        <v>0</v>
+      </c>
+      <c r="J169" s="38">
+        <v>0</v>
+      </c>
+      <c r="K169" s="37">
+        <f t="shared" ref="K169:K174" si="42">L169/F169</f>
+        <v>0</v>
+      </c>
+      <c r="L169" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="33">
+        <v>2</v>
+      </c>
+      <c r="B170" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="C170" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D170" s="36">
+        <v>1021</v>
+      </c>
+      <c r="E170" s="36">
+        <v>0.9</v>
+      </c>
+      <c r="F170" s="36">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="H169" s="38">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="I169" s="37">
+        <v>918.9</v>
+      </c>
+      <c r="G170" s="37">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="J169" s="38">
-        <v>0</v>
-      </c>
-      <c r="K169" s="37">
+      <c r="H170" s="38">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="I170" s="37">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="L169" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="B170" s="40" t="s">
-        <v>191</v>
-      </c>
-      <c r="C170" s="41">
-        <v>0</v>
-      </c>
-      <c r="D170" s="42"/>
-      <c r="E170" s="42"/>
-      <c r="F170" s="42"/>
-      <c r="G170" s="43"/>
-      <c r="H170" s="44"/>
-      <c r="I170" s="43"/>
-      <c r="J170" s="44"/>
-      <c r="K170" s="43"/>
-      <c r="L170" s="44">
+      <c r="J170" s="38">
+        <v>0</v>
+      </c>
+      <c r="K170" s="37">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="L170" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A171" s="33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B171" s="34" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C171" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D171" s="36">
-        <v>1437.8</v>
+        <v>1021</v>
       </c>
       <c r="E171" s="36">
-        <v>6.9748000000000001</v>
+        <v>7.0768000000000004</v>
       </c>
       <c r="F171" s="36">
-        <f>+E171*D171</f>
-        <v>10028.36744</v>
+        <f t="shared" si="39"/>
+        <v>7225.4128000000001</v>
       </c>
       <c r="G171" s="37">
-        <f>I171+K171</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="H171" s="38">
-        <f>J171+L171</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="I171" s="37">
-        <f>J171/F171</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="J171" s="38">
         <v>0</v>
       </c>
       <c r="K171" s="37">
-        <f>L171/F171</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L171" s="38">
@@ -7929,526 +7926,505 @@
     </row>
     <row r="172" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A172" s="33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B172" s="34" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C172" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D172" s="36">
-        <v>1437.8</v>
+        <v>1021</v>
       </c>
       <c r="E172" s="36">
-        <v>2.2624</v>
+        <v>4.7420599999999986</v>
       </c>
       <c r="F172" s="36">
-        <f>+E172*D172</f>
-        <v>3252.8787199999997</v>
+        <f t="shared" si="39"/>
+        <v>4841.6432599999989</v>
       </c>
       <c r="G172" s="37">
-        <f>I172+K172</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="H172" s="38">
-        <f>J172+L172</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="I172" s="37">
-        <f>J172/F172</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="J172" s="38">
         <v>0</v>
       </c>
       <c r="K172" s="37">
-        <f>L172/F172</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L172" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="B173" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="C173" s="41">
-        <v>0</v>
-      </c>
-      <c r="D173" s="42"/>
-      <c r="E173" s="42"/>
-      <c r="F173" s="42"/>
-      <c r="G173" s="43"/>
-      <c r="H173" s="44"/>
-      <c r="I173" s="43"/>
-      <c r="J173" s="44"/>
-      <c r="K173" s="43"/>
-      <c r="L173" s="44">
+    <row r="173" spans="1:12" s="39" customFormat="1" ht="43.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="33">
+        <v>5</v>
+      </c>
+      <c r="B173" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="C173" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D173" s="36">
+        <v>1021</v>
+      </c>
+      <c r="E173" s="36">
+        <v>7.1267799999999992</v>
+      </c>
+      <c r="F173" s="36">
+        <f t="shared" si="39"/>
+        <v>7276.4423799999995</v>
+      </c>
+      <c r="G173" s="37">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="H173" s="38">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="I173" s="37">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="J173" s="38">
+        <v>0</v>
+      </c>
+      <c r="K173" s="37">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="L173" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A174" s="33">
+        <v>6</v>
+      </c>
+      <c r="B174" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C174" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D174" s="36">
+        <v>1021</v>
+      </c>
+      <c r="E174" s="36">
+        <v>1.7259199999999999</v>
+      </c>
+      <c r="F174" s="36">
+        <f t="shared" si="39"/>
+        <v>1762.1643199999999</v>
+      </c>
+      <c r="G174" s="37">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="H174" s="38">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="I174" s="37">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="J174" s="38">
+        <v>0</v>
+      </c>
+      <c r="K174" s="37">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="L174" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B175" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="C175" s="41">
+        <v>0</v>
+      </c>
+      <c r="D175" s="42"/>
+      <c r="E175" s="42"/>
+      <c r="F175" s="42"/>
+      <c r="G175" s="43"/>
+      <c r="H175" s="44"/>
+      <c r="I175" s="43"/>
+      <c r="J175" s="44"/>
+      <c r="K175" s="43"/>
+      <c r="L175" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="33">
         <v>1</v>
       </c>
-      <c r="B174" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="C174" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D174" s="36">
-        <v>3482.3</v>
-      </c>
-      <c r="E174" s="36">
-        <v>0.9</v>
-      </c>
-      <c r="F174" s="36">
-        <f>+E174*D174</f>
-        <v>3134.07</v>
-      </c>
-      <c r="G174" s="37">
-        <f>I174+K174</f>
-        <v>0</v>
-      </c>
-      <c r="H174" s="38">
-        <f>J174+L174</f>
-        <v>0</v>
-      </c>
-      <c r="I174" s="37">
-        <f>J174/F174</f>
-        <v>0</v>
-      </c>
-      <c r="J174" s="38">
-        <v>0</v>
-      </c>
-      <c r="K174" s="37">
-        <f>L174/F174</f>
-        <v>0</v>
-      </c>
-      <c r="L174" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="33">
+      <c r="B176" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="C176" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D176" s="36">
+        <v>1437.8</v>
+      </c>
+      <c r="E176" s="36">
+        <v>6.9748000000000001</v>
+      </c>
+      <c r="F176" s="36">
+        <f>+E176*D176</f>
+        <v>10028.36744</v>
+      </c>
+      <c r="G176" s="37">
+        <f>I176+K176</f>
+        <v>0</v>
+      </c>
+      <c r="H176" s="38">
+        <f>J176+L176</f>
+        <v>0</v>
+      </c>
+      <c r="I176" s="37">
+        <f>J176/F176</f>
+        <v>0</v>
+      </c>
+      <c r="J176" s="38">
+        <v>0</v>
+      </c>
+      <c r="K176" s="37">
+        <f>L176/F176</f>
+        <v>0</v>
+      </c>
+      <c r="L176" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="33">
         <v>2</v>
       </c>
-      <c r="B175" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="C175" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D175" s="36">
-        <v>3482.3</v>
-      </c>
-      <c r="E175" s="36">
-        <v>1.2692000000000001</v>
-      </c>
-      <c r="F175" s="36">
-        <f>+E175*D175</f>
-        <v>4419.7351600000002</v>
-      </c>
-      <c r="G175" s="37">
-        <f>I175+K175</f>
-        <v>0</v>
-      </c>
-      <c r="H175" s="38">
-        <f>J175+L175</f>
-        <v>0</v>
-      </c>
-      <c r="I175" s="37">
-        <f>J175/F175</f>
-        <v>0</v>
-      </c>
-      <c r="J175" s="38">
-        <v>0</v>
-      </c>
-      <c r="K175" s="37">
-        <f>L175/F175</f>
-        <v>0</v>
-      </c>
-      <c r="L175" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="B176" s="40" t="s">
+      <c r="B177" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="C176" s="41">
-        <v>0</v>
-      </c>
-      <c r="D176" s="42"/>
-      <c r="E176" s="42"/>
-      <c r="F176" s="42"/>
-      <c r="G176" s="43"/>
-      <c r="H176" s="44"/>
-      <c r="I176" s="43"/>
-      <c r="J176" s="44"/>
-      <c r="K176" s="43"/>
-      <c r="L176" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="33">
-        <v>1</v>
-      </c>
-      <c r="B177" s="34" t="s">
+      <c r="C177" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D177" s="36">
+        <v>1437.8</v>
+      </c>
+      <c r="E177" s="36">
+        <v>2.2624</v>
+      </c>
+      <c r="F177" s="36">
+        <f>+E177*D177</f>
+        <v>3252.8787199999997</v>
+      </c>
+      <c r="G177" s="37">
+        <f>I177+K177</f>
+        <v>0</v>
+      </c>
+      <c r="H177" s="38">
+        <f>J177+L177</f>
+        <v>0</v>
+      </c>
+      <c r="I177" s="37">
+        <f>J177/F177</f>
+        <v>0</v>
+      </c>
+      <c r="J177" s="38">
+        <v>0</v>
+      </c>
+      <c r="K177" s="37">
+        <f>L177/F177</f>
+        <v>0</v>
+      </c>
+      <c r="L177" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="C177" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D177" s="36">
-        <v>24</v>
-      </c>
-      <c r="E177" s="36">
-        <v>8.9600000000000009</v>
-      </c>
-      <c r="F177" s="36">
-        <f t="shared" ref="F177:F183" si="42">+E177*D177</f>
-        <v>215.04000000000002</v>
-      </c>
-      <c r="G177" s="37">
-        <f t="shared" ref="G177:H183" si="43">I177+K177</f>
-        <v>0</v>
-      </c>
-      <c r="H177" s="38">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="I177" s="37">
-        <f t="shared" ref="I177:I183" si="44">J177/F177</f>
-        <v>0</v>
-      </c>
-      <c r="J177" s="38">
-        <v>0</v>
-      </c>
-      <c r="K177" s="37">
-        <f t="shared" ref="K177:K183" si="45">L177/F177</f>
-        <v>0</v>
-      </c>
-      <c r="L177" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="33">
-        <v>2</v>
-      </c>
-      <c r="B178" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="C178" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="D178" s="36">
-        <v>46</v>
-      </c>
-      <c r="E178" s="36">
-        <v>1.63</v>
-      </c>
-      <c r="F178" s="36">
-        <f t="shared" si="42"/>
-        <v>74.97999999999999</v>
-      </c>
-      <c r="G178" s="37">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H178" s="38">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="I178" s="37">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="J178" s="38">
-        <v>0</v>
-      </c>
-      <c r="K178" s="37">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L178" s="38">
+      <c r="B178" s="40" t="s">
+        <v>201</v>
+      </c>
+      <c r="C178" s="41">
+        <v>0</v>
+      </c>
+      <c r="D178" s="42"/>
+      <c r="E178" s="42"/>
+      <c r="F178" s="42"/>
+      <c r="G178" s="43"/>
+      <c r="H178" s="44"/>
+      <c r="I178" s="43"/>
+      <c r="J178" s="44"/>
+      <c r="K178" s="43"/>
+      <c r="L178" s="44">
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A179" s="33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B179" s="34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C179" s="35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D179" s="36">
-        <v>0.7</v>
+        <v>3482.3</v>
       </c>
       <c r="E179" s="36">
-        <v>124.1</v>
+        <v>0.9</v>
       </c>
       <c r="F179" s="36">
-        <f t="shared" si="42"/>
-        <v>86.86999999999999</v>
+        <f>+E179*D179</f>
+        <v>3134.07</v>
       </c>
       <c r="G179" s="37">
-        <f t="shared" si="43"/>
+        <f>I179+K179</f>
         <v>0</v>
       </c>
       <c r="H179" s="38">
-        <f t="shared" si="43"/>
+        <f>J179+L179</f>
         <v>0</v>
       </c>
       <c r="I179" s="37">
-        <f t="shared" si="44"/>
+        <f>J179/F179</f>
         <v>0</v>
       </c>
       <c r="J179" s="38">
         <v>0</v>
       </c>
       <c r="K179" s="37">
-        <f t="shared" si="45"/>
+        <f>L179/F179</f>
         <v>0</v>
       </c>
       <c r="L179" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A180" s="33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B180" s="34" t="s">
-        <v>97</v>
+        <v>203</v>
       </c>
       <c r="C180" s="35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D180" s="36">
-        <v>10.5</v>
+        <v>3482.3</v>
       </c>
       <c r="E180" s="36">
-        <v>52.936000000000007</v>
+        <v>1.2692000000000001</v>
       </c>
       <c r="F180" s="36">
-        <f t="shared" si="42"/>
-        <v>555.82800000000009</v>
+        <f>+E180*D180</f>
+        <v>4419.7351600000002</v>
       </c>
       <c r="G180" s="37">
-        <f t="shared" si="43"/>
+        <f>I180+K180</f>
         <v>0</v>
       </c>
       <c r="H180" s="38">
-        <f t="shared" si="43"/>
+        <f>J180+L180</f>
         <v>0</v>
       </c>
       <c r="I180" s="37">
-        <f t="shared" si="44"/>
+        <f>J180/F180</f>
         <v>0</v>
       </c>
       <c r="J180" s="38">
         <v>0</v>
       </c>
       <c r="K180" s="37">
-        <f t="shared" si="45"/>
+        <f>L180/F180</f>
         <v>0</v>
       </c>
       <c r="L180" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="33">
-        <v>5</v>
-      </c>
-      <c r="B181" s="34" t="s">
-        <v>202</v>
-      </c>
-      <c r="C181" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D181" s="36">
-        <v>26</v>
-      </c>
-      <c r="E181" s="36">
-        <v>10.8202</v>
-      </c>
-      <c r="F181" s="36">
-        <f t="shared" si="42"/>
-        <v>281.3252</v>
-      </c>
-      <c r="G181" s="37">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H181" s="38">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="I181" s="37">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="J181" s="38">
-        <v>0</v>
-      </c>
-      <c r="K181" s="37">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L181" s="38">
+    <row r="181" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="B181" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="C181" s="41">
+        <v>0</v>
+      </c>
+      <c r="D181" s="42"/>
+      <c r="E181" s="42"/>
+      <c r="F181" s="42"/>
+      <c r="G181" s="43"/>
+      <c r="H181" s="44"/>
+      <c r="I181" s="43"/>
+      <c r="J181" s="44"/>
+      <c r="K181" s="43"/>
+      <c r="L181" s="44">
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A182" s="33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C182" s="35" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D182" s="36">
-        <v>21</v>
+        <v>0.32</v>
       </c>
       <c r="E182" s="36">
-        <v>12.115600000000001</v>
+        <v>143.8486</v>
       </c>
       <c r="F182" s="36">
-        <f t="shared" si="42"/>
-        <v>254.42760000000001</v>
+        <f>+E182*D182</f>
+        <v>46.031552000000005</v>
       </c>
       <c r="G182" s="37">
+        <f>I182+K182</f>
+        <v>0</v>
+      </c>
+      <c r="H182" s="38">
+        <f>J182+L182</f>
+        <v>0</v>
+      </c>
+      <c r="I182" s="37">
+        <f>J182/F182</f>
+        <v>0</v>
+      </c>
+      <c r="J182" s="38">
+        <v>0</v>
+      </c>
+      <c r="K182" s="37">
+        <f>L182/F182</f>
+        <v>0</v>
+      </c>
+      <c r="L182" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="B183" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="C183" s="41">
+        <v>0</v>
+      </c>
+      <c r="D183" s="42"/>
+      <c r="E183" s="42"/>
+      <c r="F183" s="42"/>
+      <c r="G183" s="43"/>
+      <c r="H183" s="44"/>
+      <c r="I183" s="43"/>
+      <c r="J183" s="44"/>
+      <c r="K183" s="43"/>
+      <c r="L183" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="33">
+        <v>1</v>
+      </c>
+      <c r="B184" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C184" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D184" s="36">
+        <v>17.66</v>
+      </c>
+      <c r="E184" s="36">
+        <v>5.4732580000000004</v>
+      </c>
+      <c r="F184" s="36">
+        <f>+E184*D184</f>
+        <v>96.657736280000009</v>
+      </c>
+      <c r="G184" s="37">
+        <f t="shared" ref="G184:H186" si="43">I184+K184</f>
+        <v>0</v>
+      </c>
+      <c r="H184" s="38">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="H182" s="38">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="I182" s="37">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="J182" s="38">
-        <v>0</v>
-      </c>
-      <c r="K182" s="37">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L182" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="33">
-        <v>7</v>
-      </c>
-      <c r="B183" s="34" t="s">
-        <v>204</v>
-      </c>
-      <c r="C183" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D183" s="36">
-        <v>21</v>
-      </c>
-      <c r="E183" s="36">
-        <v>5.6794000000000011</v>
-      </c>
-      <c r="F183" s="36">
-        <f t="shared" si="42"/>
-        <v>119.26740000000002</v>
-      </c>
-      <c r="G183" s="37">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H183" s="38">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="I183" s="37">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="J183" s="38">
-        <v>0</v>
-      </c>
-      <c r="K183" s="37">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L183" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="B184" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="C184" s="41">
-        <v>0</v>
-      </c>
-      <c r="D184" s="42"/>
-      <c r="E184" s="42"/>
-      <c r="F184" s="42"/>
-      <c r="G184" s="43"/>
-      <c r="H184" s="44"/>
-      <c r="I184" s="43"/>
-      <c r="J184" s="44"/>
-      <c r="K184" s="43"/>
-      <c r="L184" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="I184" s="37">
+        <f>J184/F184</f>
+        <v>0</v>
+      </c>
+      <c r="J184" s="38">
+        <v>0</v>
+      </c>
+      <c r="K184" s="37">
+        <f>L184/F184</f>
+        <v>0</v>
+      </c>
+      <c r="L184" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A185" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B185" s="34" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C185" s="35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D185" s="36">
-        <v>0.32</v>
+        <v>17.66</v>
       </c>
       <c r="E185" s="36">
-        <v>143.8486</v>
+        <v>1.4770000000000001</v>
       </c>
       <c r="F185" s="36">
         <f>+E185*D185</f>
-        <v>46.031552000000005</v>
+        <v>26.083820000000003</v>
       </c>
       <c r="G185" s="37">
-        <f>I185+K185</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="H185" s="38">
-        <f>J185+L185</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="I185" s="37">
@@ -8466,277 +8442,172 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="B186" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="C186" s="41">
-        <v>0</v>
-      </c>
-      <c r="D186" s="42"/>
-      <c r="E186" s="42"/>
-      <c r="F186" s="42"/>
-      <c r="G186" s="43"/>
-      <c r="H186" s="44"/>
-      <c r="I186" s="43"/>
-      <c r="J186" s="44"/>
-      <c r="K186" s="43"/>
-      <c r="L186" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="33">
-        <v>1</v>
-      </c>
-      <c r="B187" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="C187" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D187" s="36">
+    <row r="186" spans="1:12" s="39" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="33">
+        <v>3</v>
+      </c>
+      <c r="B186" s="34" t="s">
+        <v>210</v>
+      </c>
+      <c r="C186" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D186" s="36">
         <v>17.66</v>
       </c>
-      <c r="E187" s="36">
-        <v>5.4732580000000004</v>
-      </c>
-      <c r="F187" s="36">
-        <f>+E187*D187</f>
-        <v>96.657736280000009</v>
-      </c>
-      <c r="G187" s="37">
-        <f t="shared" ref="G187:H189" si="46">I187+K187</f>
-        <v>0</v>
-      </c>
-      <c r="H187" s="38">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="I187" s="37">
-        <f>J187/F187</f>
-        <v>0</v>
-      </c>
-      <c r="J187" s="38">
-        <v>0</v>
-      </c>
-      <c r="K187" s="37">
-        <f>L187/F187</f>
-        <v>0</v>
-      </c>
-      <c r="L187" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:12" s="39" customFormat="1" ht="15.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="33">
-        <v>2</v>
-      </c>
-      <c r="B188" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="C188" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D188" s="36">
-        <v>17.66</v>
-      </c>
-      <c r="E188" s="36">
-        <v>1.4770000000000001</v>
-      </c>
-      <c r="F188" s="36">
-        <f>+E188*D188</f>
-        <v>26.083820000000003</v>
-      </c>
-      <c r="G188" s="37">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="H188" s="38">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="I188" s="37">
-        <f>J188/F188</f>
-        <v>0</v>
-      </c>
-      <c r="J188" s="38">
-        <v>0</v>
-      </c>
-      <c r="K188" s="37">
-        <f>L188/F188</f>
-        <v>0</v>
-      </c>
-      <c r="L188" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:12" s="46" customFormat="1" ht="28.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A189" s="33">
-        <v>3</v>
-      </c>
-      <c r="B189" s="34" t="s">
+      <c r="E186" s="36">
+        <v>210.52600000000001</v>
+      </c>
+      <c r="F186" s="36">
+        <f>+E186*D186</f>
+        <v>3717.8891600000002</v>
+      </c>
+      <c r="G186" s="37">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="H186" s="38">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="I186" s="37">
+        <f>J186/F186</f>
+        <v>0</v>
+      </c>
+      <c r="J186" s="38">
+        <v>0</v>
+      </c>
+      <c r="K186" s="37">
+        <f>L186/F186</f>
+        <v>0</v>
+      </c>
+      <c r="L186" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" s="39" customFormat="1" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="47"/>
+      <c r="B187" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="C189" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D189" s="36">
-        <v>17.66</v>
-      </c>
-      <c r="E189" s="36">
-        <v>210.52600000000001</v>
-      </c>
-      <c r="F189" s="36">
-        <f>+E189*D189</f>
-        <v>3717.8891600000002</v>
-      </c>
-      <c r="G189" s="37">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="H189" s="38">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="I189" s="37">
-        <f>J189/F189</f>
-        <v>0</v>
-      </c>
-      <c r="J189" s="38">
-        <v>0</v>
-      </c>
-      <c r="K189" s="37">
-        <f>L189/F189</f>
-        <v>0</v>
-      </c>
-      <c r="L189" s="38">
-        <v>0</v>
-      </c>
+      <c r="C187" s="51"/>
+      <c r="D187" s="52"/>
+      <c r="E187" s="52"/>
+      <c r="F187" s="52">
+        <f>SUM(F10:F186)*1.8%</f>
+        <v>8329.5974803154459</v>
+      </c>
+      <c r="G187" s="37"/>
+      <c r="H187" s="38"/>
+      <c r="I187" s="37"/>
+      <c r="J187" s="38"/>
+      <c r="K187" s="37"/>
+      <c r="L187" s="38"/>
+    </row>
+    <row r="188" spans="1:12" s="39" customFormat="1" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="47"/>
+      <c r="B188" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="C188" s="51"/>
+      <c r="D188" s="52"/>
+      <c r="E188" s="52"/>
+      <c r="F188" s="52">
+        <f>SUM(F10:F187)*2%</f>
+        <v>9421.7002610679156</v>
+      </c>
+      <c r="G188" s="37"/>
+      <c r="H188" s="38"/>
+      <c r="I188" s="37"/>
+      <c r="J188" s="38"/>
+      <c r="K188" s="37"/>
+      <c r="L188" s="38"/>
+    </row>
+    <row r="189" spans="1:12" s="46" customFormat="1" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A189" s="47"/>
+      <c r="B189" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C189" s="54"/>
+      <c r="D189" s="55"/>
+      <c r="E189" s="55"/>
+      <c r="F189" s="55">
+        <f>SUM(F10:F188)</f>
+        <v>480506.71331446362</v>
+      </c>
+      <c r="G189" s="56"/>
+      <c r="H189" s="55"/>
+      <c r="I189" s="56"/>
+      <c r="J189" s="55"/>
+      <c r="K189" s="56"/>
+      <c r="L189" s="55"/>
     </row>
     <row r="190" spans="1:12" s="39" customFormat="1" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A190" s="47"/>
-      <c r="B190" s="50" t="s">
-        <v>212</v>
-      </c>
-      <c r="C190" s="51"/>
-      <c r="D190" s="52"/>
-      <c r="E190" s="52"/>
-      <c r="F190" s="52">
-        <f>SUM(F10:F189)*1.8%</f>
-        <v>8395.2803419034462</v>
-      </c>
-      <c r="G190" s="37"/>
-      <c r="H190" s="38"/>
-      <c r="I190" s="37"/>
-      <c r="J190" s="38"/>
-      <c r="K190" s="37"/>
-      <c r="L190" s="38"/>
+      <c r="B190" s="53" t="s">
+        <v>214</v>
+      </c>
+      <c r="C190" s="54"/>
+      <c r="D190" s="55"/>
+      <c r="E190" s="55"/>
+      <c r="F190" s="55">
+        <f>F189*18%</f>
+        <v>86491.208396603441</v>
+      </c>
+      <c r="G190" s="56"/>
+      <c r="H190" s="55"/>
+      <c r="I190" s="56"/>
+      <c r="J190" s="55"/>
+      <c r="K190" s="56"/>
+      <c r="L190" s="55"/>
     </row>
     <row r="191" spans="1:12" s="39" customFormat="1" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A191" s="47"/>
-      <c r="B191" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="C191" s="51"/>
-      <c r="D191" s="52"/>
-      <c r="E191" s="52"/>
-      <c r="F191" s="52">
-        <f>SUM(F10:F190)*2%</f>
-        <v>9495.9948756196754</v>
-      </c>
-      <c r="G191" s="37"/>
-      <c r="H191" s="38"/>
-      <c r="I191" s="37"/>
-      <c r="J191" s="38"/>
-      <c r="K191" s="37"/>
-      <c r="L191" s="38"/>
-    </row>
-    <row r="192" spans="1:12" s="39" customFormat="1" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="47"/>
-      <c r="B192" s="53" t="s">
-        <v>214</v>
-      </c>
-      <c r="C192" s="54"/>
-      <c r="D192" s="55"/>
-      <c r="E192" s="55"/>
-      <c r="F192" s="55">
-        <f>SUM(F10:F191)</f>
-        <v>484295.73865660338</v>
-      </c>
-      <c r="G192" s="56"/>
-      <c r="H192" s="55"/>
-      <c r="I192" s="56"/>
-      <c r="J192" s="55"/>
-      <c r="K192" s="56"/>
-      <c r="L192" s="55"/>
-    </row>
-    <row r="193" spans="1:12" s="39" customFormat="1" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="47"/>
-      <c r="B193" s="53" t="s">
+      <c r="B191" s="53" t="s">
         <v>215</v>
       </c>
-      <c r="C193" s="54"/>
-      <c r="D193" s="55"/>
-      <c r="E193" s="55"/>
-      <c r="F193" s="55">
-        <f>F192*18%</f>
-        <v>87173.232958188601</v>
-      </c>
-      <c r="G193" s="56"/>
-      <c r="H193" s="55"/>
-      <c r="I193" s="56"/>
-      <c r="J193" s="55"/>
-      <c r="K193" s="56"/>
-      <c r="L193" s="55"/>
-    </row>
-    <row r="194" spans="1:12" s="39" customFormat="1" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="47"/>
-      <c r="B194" s="53" t="s">
+      <c r="C191" s="54"/>
+      <c r="D191" s="55"/>
+      <c r="E191" s="55"/>
+      <c r="F191" s="55">
+        <f>F189+F190</f>
+        <v>566997.92171106709</v>
+      </c>
+      <c r="G191" s="56"/>
+      <c r="H191" s="55"/>
+      <c r="I191" s="56"/>
+      <c r="J191" s="55"/>
+      <c r="K191" s="56"/>
+      <c r="L191" s="55"/>
+    </row>
+    <row r="192" spans="1:12" s="39" customFormat="1" ht="13.2" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="1:6" s="39" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="58"/>
+      <c r="B193" s="59" t="s">
         <v>216</v>
       </c>
-      <c r="C194" s="54"/>
-      <c r="D194" s="55"/>
-      <c r="E194" s="55"/>
-      <c r="F194" s="55">
-        <f>F192+F193</f>
-        <v>571468.97161479201</v>
-      </c>
-      <c r="G194" s="56"/>
-      <c r="H194" s="55"/>
-      <c r="I194" s="56"/>
-      <c r="J194" s="55"/>
-      <c r="K194" s="56"/>
-      <c r="L194" s="55"/>
-    </row>
-    <row r="195" spans="1:12" s="39" customFormat="1" ht="13.2" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="1:12" s="39" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="58"/>
-      <c r="B196" s="59" t="s">
+      <c r="C193" s="59"/>
+      <c r="D193" s="59"/>
+      <c r="E193" s="60"/>
+      <c r="F193" s="63" t="s">
         <v>217</v>
       </c>
-      <c r="C196" s="59"/>
-      <c r="D196" s="59"/>
-      <c r="E196" s="60"/>
-      <c r="F196" s="63" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="197" spans="1:12" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="1:12" s="45" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" spans="1:12" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="1:12" s="39" customFormat="1" ht="13.2" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="1:12" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="1:12" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="1:12" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="1:12" s="39" customFormat="1" ht="13.2" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="1:12" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="1:12" s="39" customFormat="1" ht="13.2" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="1:12" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="1:12" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="194" spans="1:6" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="1:6" s="39" customFormat="1" ht="13.2" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="1:6" s="39" customFormat="1" ht="13.2" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="1:6" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="1:6" s="45" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" spans="1:6" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="1:6" s="39" customFormat="1" ht="13.2" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="1:6" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="1:6" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="1:6" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="1:6" s="39" customFormat="1" ht="13.2" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="1:6" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="1:6" s="39" customFormat="1" ht="13.2" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="1:6" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="1:6" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="209" s="39" customFormat="1" ht="27.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="210" s="39" customFormat="1" ht="41.7" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="211" s="45" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
